--- a/Aepms-backend/data/ae_shop_trial.xlsx
+++ b/Aepms-backend/data/ae_shop_trial.xlsx
@@ -1,41 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ozellar_project\Aepms-backend\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOKUL\Desktop\Ozellar_project\Aepms-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820CE369-6E08-4837-85CC-3F61781B5CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C188E8-4336-4AE3-AB76-072E20534FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{385394E6-7E2A-4385-A13A-ED5A84619683}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vessel_generators" sheetId="1" r:id="rId1"/>
     <sheet name="generator_baseline_data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="42">
   <si>
     <t>imo_number</t>
   </si>
@@ -59,33 +45,6 @@
   </si>
   <si>
     <t>rated_speed_rpm</t>
-  </si>
-  <si>
-    <t>load_kw</t>
-  </si>
-  <si>
-    <t>pmax_raw_mpa</t>
-  </si>
-  <si>
-    <t>boost_air_pressure_raw_mpa</t>
-  </si>
-  <si>
-    <t>exh_temp_tc_inlet_graph_c</t>
-  </si>
-  <si>
-    <t>exh_temp_cyl_outlet_avg_graph_c</t>
-  </si>
-  <si>
-    <t>exh_temp_tc_outlet_graph_c</t>
-  </si>
-  <si>
-    <t>fuel_pump_index_graph</t>
-  </si>
-  <si>
-    <t>sfoc_graph_g_kwh</t>
-  </si>
-  <si>
-    <t>load_percentage</t>
   </si>
   <si>
     <t>Aux Engine No.1</t>
@@ -118,7 +77,7 @@
     <t>AQ6K201752</t>
   </si>
   <si>
-    <t>DE618Z3128</t>
+    <t>DE618Z1404</t>
   </si>
   <si>
     <t>DAIHATSU</t>
@@ -127,19 +86,64 @@
     <t>6DE-18</t>
   </si>
   <si>
+    <t>DE618Z1405</t>
+  </si>
+  <si>
+    <t>DE618Z1406</t>
+  </si>
+  <si>
+    <t>DE618Z3128</t>
+  </si>
+  <si>
     <t>DE618Z3129</t>
   </si>
   <si>
     <t>DE618Z3130</t>
   </si>
   <si>
-    <t>DE618Z1404</t>
+    <t>AQ6K201753</t>
   </si>
   <si>
-    <t>DE618Z1405</t>
+    <t>AQ6K201754</t>
   </si>
   <si>
-    <t>DE618Z1406</t>
+    <t>AQ6K201755</t>
+  </si>
+  <si>
+    <t>DE618Z2133</t>
+  </si>
+  <si>
+    <t>DE618Z2134</t>
+  </si>
+  <si>
+    <t>DE618Z2135</t>
+  </si>
+  <si>
+    <t>load_percentage</t>
+  </si>
+  <si>
+    <t>load_kw</t>
+  </si>
+  <si>
+    <t>pmax_raw_mpa</t>
+  </si>
+  <si>
+    <t>boost_air_pressure_raw_mpa</t>
+  </si>
+  <si>
+    <t>exh_temp_tc_inlet_graph_c</t>
+  </si>
+  <si>
+    <t>exh_temp_cyl_outlet_avg_graph_c</t>
+  </si>
+  <si>
+    <t>exh_temp_tc_outlet_graph_c</t>
+  </si>
+  <si>
+    <t>fuel_pump_index_graph</t>
+  </si>
+  <si>
+    <t>sfoc_graph_g_kwh</t>
   </si>
   <si>
     <t>Not Available</t>
@@ -228,13 +232,11 @@
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
@@ -257,37 +259,37 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{30E66E99-235F-4C53-844C-904FDC360872}" name="Table1" displayName="Table1" ref="A1:H13" totalsRowShown="0">
-  <autoFilter ref="A1:H13" xr:uid="{30E66E99-235F-4C53-844C-904FDC360872}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:H13" totalsRowShown="0">
+  <autoFilter ref="A1:H13" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{67DF893F-13BA-4845-90C2-5D9285DDB8E1}" name="imo_number"/>
-    <tableColumn id="2" xr3:uid="{64625298-2E8B-43C6-B193-D95A038E089D}" name="engine_no"/>
-    <tableColumn id="3" xr3:uid="{30924F9B-403D-4727-894A-C1EFD1B09700}" name="designation"/>
-    <tableColumn id="4" xr3:uid="{5E3F826D-0E1F-4C25-B93B-49569499A33A}" name="maker"/>
-    <tableColumn id="5" xr3:uid="{7882E201-8245-4C9B-A453-D83867EC8DA2}" name="model"/>
-    <tableColumn id="6" xr3:uid="{E8B6BB17-843E-44CF-BACA-176453A10C38}" name="num_of_cylinders"/>
-    <tableColumn id="7" xr3:uid="{3319D750-8C23-4E54-A5FB-038914502DFC}" name="rated_engine_output_kw"/>
-    <tableColumn id="8" xr3:uid="{E439295F-DBA5-4433-AADA-5427F081E404}" name="rated_speed_rpm"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="imo_number"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="engine_no"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="designation"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="maker"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="model"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="num_of_cylinders"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="rated_engine_output_kw"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="rated_speed_rpm"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E246DAAE-4513-41D3-86E4-A73AD6FB1861}" name="Table3" displayName="Table3" ref="A1:K16" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:K16" xr:uid="{E246DAAE-4513-41D3-86E4-A73AD6FB1861}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table3" displayName="Table3" ref="A1:K16" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:K16" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4A5BC75F-5D7F-4CB7-978B-B2AEE585E5E5}" name="imo_number"/>
-    <tableColumn id="11" xr3:uid="{FE80152D-C5AD-42C1-B26A-1F4327DDE9D0}" name="engine_no"/>
-    <tableColumn id="2" xr3:uid="{0620CE8D-4EA5-4C49-BB50-8D29D25B7492}" name="load_percentage"/>
-    <tableColumn id="3" xr3:uid="{0F53CCB9-4E21-45F0-950F-3D7C62755E36}" name="load_kw"/>
-    <tableColumn id="4" xr3:uid="{00C8B840-6B4B-4F12-BED5-F3B79F4C9BA8}" name="pmax_raw_mpa"/>
-    <tableColumn id="5" xr3:uid="{21A0402C-3327-4658-9A9A-2D5379F84C80}" name="boost_air_pressure_raw_mpa"/>
-    <tableColumn id="6" xr3:uid="{291C3543-7CB7-4492-A6E8-CF543E6FB0F2}" name="exh_temp_tc_inlet_graph_c"/>
-    <tableColumn id="7" xr3:uid="{92ED21BB-F20F-4C5D-A7F0-97DD40B3A101}" name="exh_temp_cyl_outlet_avg_graph_c"/>
-    <tableColumn id="8" xr3:uid="{5612C3CD-A929-439E-8A68-03A51784B31F}" name="exh_temp_tc_outlet_graph_c"/>
-    <tableColumn id="9" xr3:uid="{00DA0E18-5649-48B4-81E3-AE91A6E55165}" name="fuel_pump_index_graph"/>
-    <tableColumn id="10" xr3:uid="{12C90C99-3535-4A90-8D35-F09AB44C9F10}" name="sfoc_graph_g_kwh"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="imo_number"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="engine_no"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="load_percentage"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="load_kw"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="pmax_raw_mpa"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="boost_air_pressure_raw_mpa"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="exh_temp_tc_inlet_graph_c"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="exh_temp_cyl_outlet_avg_graph_c"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="exh_temp_tc_outlet_graph_c"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="fuel_pump_index_graph"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="sfoc_graph_g_kwh"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -609,8 +611,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E80DD266-46B5-4FDB-AA20-E9283946F305}">
-  <dimension ref="A1:H19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
@@ -657,13 +659,13 @@
         <v>11988</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>6</v>
@@ -683,13 +685,13 @@
         <v>11989</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -709,13 +711,13 @@
         <v>11990</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>6</v>
@@ -732,16 +734,16 @@
         <v>9832913</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>6</v>
@@ -758,16 +760,16 @@
         <v>9832913</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F6">
         <v>6</v>
@@ -784,16 +786,16 @@
         <v>9832913</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -813,13 +815,13 @@
         <v>11597</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2">
         <v>6</v>
@@ -839,13 +841,13 @@
         <v>11598</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2">
         <v>6</v>
@@ -865,13 +867,13 @@
         <v>11599</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F10" s="2">
         <v>6</v>
@@ -888,16 +890,16 @@
         <v>9481659</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -914,16 +916,16 @@
         <v>9481659</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
         <v>20</v>
-      </c>
-      <c r="D12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" t="s">
-        <v>29</v>
       </c>
       <c r="F12">
         <v>6</v>
@@ -940,16 +942,16 @@
         <v>9481659</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F13">
         <v>6</v>
@@ -966,16 +968,16 @@
         <v>9481219</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F14">
         <v>6</v>
@@ -992,16 +994,16 @@
         <v>9481219</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" t="s">
         <v>20</v>
-      </c>
-      <c r="D15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" t="s">
-        <v>29</v>
       </c>
       <c r="F15">
         <v>6</v>
@@ -1018,16 +1020,16 @@
         <v>9481219</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F16">
         <v>6</v>
@@ -1047,13 +1049,13 @@
         <v>11594</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -1073,13 +1075,13 @@
         <v>11595</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F18">
         <v>6</v>
@@ -1099,13 +1101,13 @@
         <v>11596</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F19">
         <v>6</v>
@@ -1117,18 +1119,174 @@
         <v>900</v>
       </c>
     </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>9832925</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20">
+        <v>6</v>
+      </c>
+      <c r="G20">
+        <v>900</v>
+      </c>
+      <c r="H20">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>9832925</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21">
+        <v>6</v>
+      </c>
+      <c r="G21">
+        <v>900</v>
+      </c>
+      <c r="H21">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>9832925</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22">
+        <v>6</v>
+      </c>
+      <c r="G22">
+        <v>900</v>
+      </c>
+      <c r="H22">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>9792058</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23">
+        <v>6</v>
+      </c>
+      <c r="G23">
+        <v>660</v>
+      </c>
+      <c r="H23">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>9792058</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24">
+        <v>6</v>
+      </c>
+      <c r="G24">
+        <v>660</v>
+      </c>
+      <c r="H24">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>9792058</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25">
+        <v>6</v>
+      </c>
+      <c r="G25">
+        <v>660</v>
+      </c>
+      <c r="H25">
+        <v>900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C88235-57D5-40DD-96FD-C9216BEFD87A}">
-  <dimension ref="A1:K91"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:K121"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13.33203125" customWidth="1"/>
@@ -1151,31 +1309,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -2233,7 +2391,7 @@
         <v>9832913</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C32" s="3">
         <v>25</v>
@@ -2247,8 +2405,8 @@
       <c r="F32" s="3">
         <v>0.04</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>35</v>
+      <c r="G32">
+        <v>208.5</v>
       </c>
       <c r="H32" s="3">
         <v>255.8</v>
@@ -2260,7 +2418,7 @@
         <v>13</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
@@ -2268,7 +2426,7 @@
         <v>9832913</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C33" s="3">
         <v>50</v>
@@ -2282,8 +2440,8 @@
       <c r="F33" s="3">
         <v>0.115</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>35</v>
+      <c r="G33">
+        <v>459.5</v>
       </c>
       <c r="H33" s="3">
         <v>264.2</v>
@@ -2295,7 +2453,7 @@
         <v>17</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -2303,7 +2461,7 @@
         <v>9832913</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C34" s="3">
         <v>75</v>
@@ -2317,8 +2475,8 @@
       <c r="F34" s="3">
         <v>0.19500000000000001</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>35</v>
+      <c r="G34">
+        <v>460.5</v>
       </c>
       <c r="H34" s="3">
         <v>278.3</v>
@@ -2330,7 +2488,7 @@
         <v>21</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
@@ -2338,7 +2496,7 @@
         <v>9832913</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C35" s="3">
         <v>100</v>
@@ -2352,8 +2510,8 @@
       <c r="F35" s="3">
         <v>0.28499999999999998</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>35</v>
+      <c r="G35">
+        <v>495.8</v>
       </c>
       <c r="H35" s="3">
         <v>318.3</v>
@@ -2373,7 +2531,7 @@
         <v>9832913</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C36" s="3">
         <v>110</v>
@@ -2387,8 +2545,8 @@
       <c r="F36" s="3">
         <v>0.30499999999999999</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>35</v>
+      <c r="G36">
+        <v>525</v>
       </c>
       <c r="H36" s="3">
         <v>331.7</v>
@@ -2400,7 +2558,7 @@
         <v>28.5</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
@@ -2408,7 +2566,7 @@
         <v>9832913</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C37" s="3">
         <v>25</v>
@@ -2422,8 +2580,8 @@
       <c r="F37" s="3">
         <v>0.04</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>35</v>
+      <c r="G37">
+        <v>208.5</v>
       </c>
       <c r="H37" s="3">
         <v>260</v>
@@ -2435,7 +2593,7 @@
         <v>13</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
@@ -2443,7 +2601,7 @@
         <v>9832913</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C38" s="3">
         <v>50</v>
@@ -2457,8 +2615,8 @@
       <c r="F38" s="3">
         <v>0.11</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>35</v>
+      <c r="G38">
+        <v>459.5</v>
       </c>
       <c r="H38" s="3">
         <v>273.3</v>
@@ -2470,7 +2628,7 @@
         <v>18</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
@@ -2478,7 +2636,7 @@
         <v>9832913</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C39" s="3">
         <v>75</v>
@@ -2492,8 +2650,8 @@
       <c r="F39" s="3">
         <v>0.19500000000000001</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>35</v>
+      <c r="G39">
+        <v>460.5</v>
       </c>
       <c r="H39" s="3">
         <v>283.3</v>
@@ -2505,7 +2663,7 @@
         <v>22</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
@@ -2513,7 +2671,7 @@
         <v>9832913</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C40" s="3">
         <v>100</v>
@@ -2527,8 +2685,8 @@
       <c r="F40" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>35</v>
+      <c r="G40">
+        <v>495.8</v>
       </c>
       <c r="H40" s="3">
         <v>323.3</v>
@@ -2548,7 +2706,7 @@
         <v>9832913</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C41" s="3">
         <v>110</v>
@@ -2562,8 +2720,8 @@
       <c r="F41" s="3">
         <v>0.31</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>35</v>
+      <c r="G41">
+        <v>525</v>
       </c>
       <c r="H41" s="3">
         <v>336.7</v>
@@ -2575,7 +2733,7 @@
         <v>29.5</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
@@ -2583,7 +2741,7 @@
         <v>9832913</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C42" s="3">
         <v>25</v>
@@ -2597,8 +2755,8 @@
       <c r="F42" s="3">
         <v>0.04</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>35</v>
+      <c r="G42">
+        <v>208.5</v>
       </c>
       <c r="H42" s="3">
         <v>256.7</v>
@@ -2610,7 +2768,7 @@
         <v>13</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
@@ -2618,7 +2776,7 @@
         <v>9832913</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C43" s="3">
         <v>50</v>
@@ -2632,8 +2790,8 @@
       <c r="F43" s="3">
         <v>0.115</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>35</v>
+      <c r="G43">
+        <v>459.5</v>
       </c>
       <c r="H43" s="3">
         <v>271.7</v>
@@ -2645,7 +2803,7 @@
         <v>18</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
@@ -2653,7 +2811,7 @@
         <v>9832913</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C44" s="3">
         <v>75</v>
@@ -2667,8 +2825,8 @@
       <c r="F44" s="3">
         <v>0.2</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>35</v>
+      <c r="G44">
+        <v>460.5</v>
       </c>
       <c r="H44" s="3">
         <v>283.3</v>
@@ -2680,7 +2838,7 @@
         <v>22</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
@@ -2688,7 +2846,7 @@
         <v>9832913</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C45" s="3">
         <v>100</v>
@@ -2702,8 +2860,8 @@
       <c r="F45" s="3">
         <v>0.3</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>35</v>
+      <c r="G45">
+        <v>495.8</v>
       </c>
       <c r="H45" s="3">
         <v>320</v>
@@ -2723,7 +2881,7 @@
         <v>9832913</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C46" s="3">
         <v>110</v>
@@ -2737,8 +2895,8 @@
       <c r="F46" s="3">
         <v>0.31</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>35</v>
+      <c r="G46">
+        <v>525</v>
       </c>
       <c r="H46" s="3">
         <v>335.8</v>
@@ -2750,7 +2908,7 @@
         <v>29</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
@@ -2758,7 +2916,7 @@
         <v>9481659</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C47">
         <v>25</v>
@@ -2793,7 +2951,7 @@
         <v>9481659</v>
       </c>
       <c r="B48" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C48">
         <v>50</v>
@@ -2828,7 +2986,7 @@
         <v>9481659</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C49">
         <v>75</v>
@@ -2863,7 +3021,7 @@
         <v>9481659</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C50">
         <v>100</v>
@@ -2898,7 +3056,7 @@
         <v>9481659</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C51">
         <v>110</v>
@@ -2933,7 +3091,7 @@
         <v>9481659</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C52">
         <v>25</v>
@@ -2968,7 +3126,7 @@
         <v>9481659</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C53">
         <v>50</v>
@@ -3003,7 +3161,7 @@
         <v>9481659</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C54">
         <v>75</v>
@@ -3038,7 +3196,7 @@
         <v>9481659</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C55">
         <v>100</v>
@@ -3073,7 +3231,7 @@
         <v>9481659</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C56">
         <v>110</v>
@@ -3108,7 +3266,7 @@
         <v>9481659</v>
       </c>
       <c r="B57" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C57">
         <v>25</v>
@@ -3143,7 +3301,7 @@
         <v>9481659</v>
       </c>
       <c r="B58" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C58">
         <v>50</v>
@@ -3178,7 +3336,7 @@
         <v>9481659</v>
       </c>
       <c r="B59" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C59">
         <v>75</v>
@@ -3213,7 +3371,7 @@
         <v>9481659</v>
       </c>
       <c r="B60" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C60">
         <v>100</v>
@@ -3248,7 +3406,7 @@
         <v>9481659</v>
       </c>
       <c r="B61" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C61">
         <v>110</v>
@@ -3283,7 +3441,7 @@
         <v>9481219</v>
       </c>
       <c r="B62" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C62">
         <v>25</v>
@@ -3318,7 +3476,7 @@
         <v>9481219</v>
       </c>
       <c r="B63" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C63">
         <v>50</v>
@@ -3353,7 +3511,7 @@
         <v>9481219</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C64">
         <v>75</v>
@@ -3388,7 +3546,7 @@
         <v>9481219</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C65">
         <v>100</v>
@@ -3423,7 +3581,7 @@
         <v>9481219</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C66">
         <v>110</v>
@@ -3458,7 +3616,7 @@
         <v>9481219</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C67">
         <v>25</v>
@@ -3493,7 +3651,7 @@
         <v>9481219</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C68">
         <v>50</v>
@@ -3528,7 +3686,7 @@
         <v>9481219</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C69">
         <v>75</v>
@@ -3563,7 +3721,7 @@
         <v>9481219</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C70">
         <v>100</v>
@@ -3598,7 +3756,7 @@
         <v>9481219</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C71">
         <v>110</v>
@@ -3633,7 +3791,7 @@
         <v>9481219</v>
       </c>
       <c r="B72" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C72">
         <v>25</v>
@@ -3668,7 +3826,7 @@
         <v>9481219</v>
       </c>
       <c r="B73" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C73">
         <v>50</v>
@@ -3703,7 +3861,7 @@
         <v>9481219</v>
       </c>
       <c r="B74" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C74">
         <v>75</v>
@@ -3738,7 +3896,7 @@
         <v>9481219</v>
       </c>
       <c r="B75" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C75">
         <v>100</v>
@@ -3773,7 +3931,7 @@
         <v>9481219</v>
       </c>
       <c r="B76" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C76">
         <v>110</v>
@@ -4328,252 +4486,989 @@
         <v>206.9</v>
       </c>
     </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>9832925</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92">
+        <v>25</v>
+      </c>
+      <c r="D92">
+        <v>225</v>
+      </c>
+      <c r="E92">
+        <v>6.1</v>
+      </c>
+      <c r="F92">
+        <v>0.04</v>
+      </c>
+      <c r="G92">
+        <v>416.5</v>
+      </c>
+      <c r="H92">
+        <v>247</v>
+      </c>
+      <c r="I92">
+        <v>300</v>
+      </c>
+      <c r="J92">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>9832925</v>
+      </c>
+      <c r="B93" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93">
+        <v>50</v>
+      </c>
+      <c r="D93">
+        <v>450</v>
+      </c>
+      <c r="E93">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F93">
+        <v>0.12</v>
+      </c>
+      <c r="G93">
+        <v>461.5</v>
+      </c>
+      <c r="H93">
+        <v>258</v>
+      </c>
+      <c r="I93">
+        <v>305</v>
+      </c>
+      <c r="J93">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>9832925</v>
+      </c>
+      <c r="B94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94">
+        <v>75</v>
+      </c>
+      <c r="D94">
+        <v>675</v>
+      </c>
+      <c r="E94">
+        <v>12.4</v>
+      </c>
+      <c r="F94">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="G94">
+        <v>471.5</v>
+      </c>
+      <c r="H94">
+        <v>283</v>
+      </c>
+      <c r="I94">
+        <v>290</v>
+      </c>
+      <c r="J94">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>9832925</v>
+      </c>
+      <c r="B95" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95">
+        <v>100</v>
+      </c>
+      <c r="D95">
+        <v>900</v>
+      </c>
+      <c r="E95">
+        <v>15.02</v>
+      </c>
+      <c r="F95">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G95">
+        <v>519.5</v>
+      </c>
+      <c r="H95">
+        <v>308</v>
+      </c>
+      <c r="I95">
+        <v>300</v>
+      </c>
+      <c r="J95">
+        <v>25</v>
+      </c>
+      <c r="K95">
+        <v>199.2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>9832925</v>
+      </c>
+      <c r="B96" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96">
+        <v>110</v>
+      </c>
+      <c r="D96">
+        <v>990</v>
+      </c>
+      <c r="E96">
+        <v>16.32</v>
+      </c>
+      <c r="F96">
+        <v>0.31</v>
+      </c>
+      <c r="G96">
+        <v>542</v>
+      </c>
+      <c r="H96">
+        <v>328</v>
+      </c>
+      <c r="I96">
+        <v>310</v>
+      </c>
+      <c r="J96">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>9832925</v>
+      </c>
+      <c r="B97" t="s">
+        <v>27</v>
+      </c>
+      <c r="C97">
+        <v>25</v>
+      </c>
+      <c r="D97">
+        <v>225</v>
+      </c>
+      <c r="E97">
+        <v>6.05</v>
+      </c>
+      <c r="F97">
+        <v>0.04</v>
+      </c>
+      <c r="G97">
+        <v>415</v>
+      </c>
+      <c r="H97">
+        <v>260</v>
+      </c>
+      <c r="I97">
+        <v>310</v>
+      </c>
+      <c r="J97">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>9832925</v>
+      </c>
+      <c r="B98" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98">
+        <v>50</v>
+      </c>
+      <c r="D98">
+        <v>450</v>
+      </c>
+      <c r="E98">
+        <v>9.1</v>
+      </c>
+      <c r="F98">
+        <v>0.115</v>
+      </c>
+      <c r="G98">
+        <v>456</v>
+      </c>
+      <c r="H98">
+        <v>264</v>
+      </c>
+      <c r="I98">
+        <v>315</v>
+      </c>
+      <c r="J98">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>9832925</v>
+      </c>
+      <c r="B99" t="s">
+        <v>27</v>
+      </c>
+      <c r="C99">
+        <v>75</v>
+      </c>
+      <c r="D99">
+        <v>675</v>
+      </c>
+      <c r="E99">
+        <v>12.38</v>
+      </c>
+      <c r="F99">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="G99">
+        <v>461.5</v>
+      </c>
+      <c r="H99">
+        <v>283</v>
+      </c>
+      <c r="I99">
+        <v>290</v>
+      </c>
+      <c r="J99">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>9832925</v>
+      </c>
+      <c r="B100" t="s">
+        <v>27</v>
+      </c>
+      <c r="C100">
+        <v>100</v>
+      </c>
+      <c r="D100">
+        <v>924</v>
+      </c>
+      <c r="E100">
+        <v>14.98</v>
+      </c>
+      <c r="F100">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G100">
+        <v>506.8</v>
+      </c>
+      <c r="H100">
+        <v>318</v>
+      </c>
+      <c r="I100">
+        <v>295</v>
+      </c>
+      <c r="J100">
+        <v>25</v>
+      </c>
+      <c r="K100">
+        <v>200.4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>9832925</v>
+      </c>
+      <c r="B101" t="s">
+        <v>27</v>
+      </c>
+      <c r="C101">
+        <v>110</v>
+      </c>
+      <c r="D101">
+        <v>990</v>
+      </c>
+      <c r="E101">
+        <v>16.32</v>
+      </c>
+      <c r="F101">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="G101">
+        <v>536</v>
+      </c>
+      <c r="H101">
+        <v>328</v>
+      </c>
+      <c r="I101">
+        <v>300</v>
+      </c>
+      <c r="J101">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>9832925</v>
+      </c>
+      <c r="B102" t="s">
+        <v>28</v>
+      </c>
+      <c r="C102">
+        <v>25</v>
+      </c>
+      <c r="D102">
+        <v>225</v>
+      </c>
+      <c r="E102">
+        <v>6.05</v>
+      </c>
+      <c r="F102">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G102">
+        <v>411.5</v>
+      </c>
+      <c r="H102">
+        <v>248</v>
+      </c>
+      <c r="I102">
+        <v>290</v>
+      </c>
+      <c r="J102">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>9832925</v>
+      </c>
+      <c r="B103" t="s">
+        <v>28</v>
+      </c>
+      <c r="C103">
+        <v>50</v>
+      </c>
+      <c r="D103">
+        <v>450</v>
+      </c>
+      <c r="E103">
+        <v>9.1</v>
+      </c>
+      <c r="F103">
+        <v>0.115</v>
+      </c>
+      <c r="G103">
+        <v>450</v>
+      </c>
+      <c r="H103">
+        <v>263</v>
+      </c>
+      <c r="I103">
+        <v>305</v>
+      </c>
+      <c r="J103">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>9832925</v>
+      </c>
+      <c r="B104" t="s">
+        <v>28</v>
+      </c>
+      <c r="C104">
+        <v>75</v>
+      </c>
+      <c r="D104">
+        <v>675</v>
+      </c>
+      <c r="E104">
+        <v>12.38</v>
+      </c>
+      <c r="F104">
+        <v>0.19</v>
+      </c>
+      <c r="G104">
+        <v>453.5</v>
+      </c>
+      <c r="H104">
+        <v>283</v>
+      </c>
+      <c r="I104">
+        <v>290</v>
+      </c>
+      <c r="J104">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>9832925</v>
+      </c>
+      <c r="B105" t="s">
+        <v>28</v>
+      </c>
+      <c r="C105">
+        <v>100</v>
+      </c>
+      <c r="D105">
+        <v>900</v>
+      </c>
+      <c r="E105">
+        <v>14.98</v>
+      </c>
+      <c r="F105">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G105">
+        <v>504.8</v>
+      </c>
+      <c r="H105">
+        <v>311</v>
+      </c>
+      <c r="I105">
+        <v>285</v>
+      </c>
+      <c r="J105">
+        <v>25</v>
+      </c>
+      <c r="K105">
+        <v>199.2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>9832925</v>
+      </c>
+      <c r="B106" t="s">
+        <v>28</v>
+      </c>
+      <c r="C106">
+        <v>110</v>
+      </c>
+      <c r="D106">
+        <v>990</v>
+      </c>
+      <c r="E106">
+        <v>16.32</v>
+      </c>
+      <c r="F106">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G106">
+        <v>534.5</v>
+      </c>
+      <c r="H106">
+        <v>328</v>
+      </c>
+      <c r="I106">
+        <v>295</v>
+      </c>
+      <c r="J106">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>9792058</v>
+      </c>
+      <c r="B107" t="s">
+        <v>29</v>
+      </c>
+      <c r="C107">
+        <v>25</v>
+      </c>
+      <c r="D107">
+        <v>153</v>
+      </c>
+      <c r="E107">
+        <v>7.25</v>
+      </c>
+      <c r="F107">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="G107">
+        <v>220</v>
+      </c>
+      <c r="H107">
+        <v>248</v>
+      </c>
+      <c r="I107">
+        <v>336</v>
+      </c>
+      <c r="J107">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>9792058</v>
+      </c>
+      <c r="B108" t="s">
+        <v>29</v>
+      </c>
+      <c r="C108">
+        <v>50</v>
+      </c>
+      <c r="D108">
+        <v>305</v>
+      </c>
+      <c r="E108">
+        <v>10.78</v>
+      </c>
+      <c r="F108">
+        <v>0.12</v>
+      </c>
+      <c r="G108">
+        <v>382.5</v>
+      </c>
+      <c r="H108">
+        <v>262</v>
+      </c>
+      <c r="I108">
+        <v>332</v>
+      </c>
+      <c r="J108">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>9792058</v>
+      </c>
+      <c r="B109" t="s">
+        <v>29</v>
+      </c>
+      <c r="C109">
+        <v>75</v>
+      </c>
+      <c r="D109">
+        <v>458</v>
+      </c>
+      <c r="E109">
+        <v>14.03</v>
+      </c>
+      <c r="F109">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="G109">
+        <v>395</v>
+      </c>
+      <c r="H109">
+        <v>283</v>
+      </c>
+      <c r="I109">
+        <v>303</v>
+      </c>
+      <c r="J109">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>9792058</v>
+      </c>
+      <c r="B110" t="s">
+        <v>29</v>
+      </c>
+      <c r="C110">
+        <v>100</v>
+      </c>
+      <c r="D110">
+        <v>610</v>
+      </c>
+      <c r="E110">
+        <v>17.38</v>
+      </c>
+      <c r="F110">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="G110">
+        <v>437.5</v>
+      </c>
+      <c r="H110">
+        <v>321</v>
+      </c>
+      <c r="I110">
+        <v>318</v>
+      </c>
+      <c r="J110">
+        <v>23.5</v>
+      </c>
+      <c r="K110">
+        <v>196.7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>9792058</v>
+      </c>
+      <c r="B111" t="s">
+        <v>29</v>
+      </c>
+      <c r="C111">
+        <v>110</v>
+      </c>
+      <c r="D111">
+        <v>671</v>
+      </c>
+      <c r="E111">
+        <v>18.28</v>
+      </c>
+      <c r="F111">
+        <v>0.308</v>
+      </c>
+      <c r="G111">
+        <v>487.5</v>
+      </c>
+      <c r="H111">
+        <v>342</v>
+      </c>
+      <c r="I111">
+        <v>333</v>
+      </c>
+      <c r="J111">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>9792058</v>
+      </c>
+      <c r="B112" t="s">
+        <v>30</v>
+      </c>
+      <c r="C112">
+        <v>25</v>
+      </c>
+      <c r="D112">
+        <v>153</v>
+      </c>
+      <c r="E112">
+        <v>7.22</v>
+      </c>
+      <c r="F112">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="G112">
+        <v>215</v>
+      </c>
+      <c r="H112">
+        <v>250</v>
+      </c>
+      <c r="I112">
+        <v>334</v>
+      </c>
+      <c r="J112">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>9792058</v>
+      </c>
+      <c r="B113" t="s">
+        <v>30</v>
+      </c>
+      <c r="C113">
+        <v>50</v>
+      </c>
+      <c r="D113">
+        <v>305</v>
+      </c>
+      <c r="E113">
+        <v>10.77</v>
+      </c>
+      <c r="F113">
+        <v>0.12</v>
+      </c>
+      <c r="G113">
+        <v>390</v>
+      </c>
+      <c r="H113">
+        <v>267</v>
+      </c>
+      <c r="I113">
+        <v>329</v>
+      </c>
+      <c r="J113">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>9792058</v>
+      </c>
+      <c r="B114" t="s">
+        <v>30</v>
+      </c>
+      <c r="C114">
+        <v>75</v>
+      </c>
+      <c r="D114">
+        <v>458</v>
+      </c>
+      <c r="E114">
+        <v>14.07</v>
+      </c>
+      <c r="F114">
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="G114">
+        <v>400</v>
+      </c>
+      <c r="H114">
+        <v>284</v>
+      </c>
+      <c r="I114">
+        <v>297</v>
+      </c>
+      <c r="J114">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>9792058</v>
+      </c>
+      <c r="B115" t="s">
+        <v>30</v>
+      </c>
+      <c r="C115">
+        <v>100</v>
+      </c>
+      <c r="D115">
+        <v>610</v>
+      </c>
+      <c r="E115">
+        <v>17.28</v>
+      </c>
+      <c r="F115">
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="G115">
+        <v>435</v>
+      </c>
+      <c r="H115">
+        <v>324</v>
+      </c>
+      <c r="I115">
+        <v>310.5</v>
+      </c>
+      <c r="J115">
+        <v>23</v>
+      </c>
+      <c r="K115">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>9792058</v>
+      </c>
+      <c r="B116" t="s">
+        <v>30</v>
+      </c>
+      <c r="C116">
+        <v>110</v>
+      </c>
+      <c r="D116">
+        <v>671</v>
+      </c>
+      <c r="E116">
+        <v>18.23</v>
+      </c>
+      <c r="F116">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="G116">
+        <v>487.5</v>
+      </c>
+      <c r="H116">
+        <v>347</v>
+      </c>
+      <c r="I116">
+        <v>328</v>
+      </c>
+      <c r="J116">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>9792058</v>
+      </c>
+      <c r="B117" t="s">
+        <v>31</v>
+      </c>
+      <c r="C117">
+        <v>25</v>
+      </c>
+      <c r="D117">
+        <v>153</v>
+      </c>
+      <c r="E117">
+        <v>7.13</v>
+      </c>
+      <c r="F117">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="G117">
+        <v>217.5</v>
+      </c>
+      <c r="H117">
+        <v>253</v>
+      </c>
+      <c r="I117">
+        <v>333</v>
+      </c>
+      <c r="J117">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>9792058</v>
+      </c>
+      <c r="B118" t="s">
+        <v>31</v>
+      </c>
+      <c r="C118">
+        <v>50</v>
+      </c>
+      <c r="D118">
+        <v>305</v>
+      </c>
+      <c r="E118">
+        <v>10.7</v>
+      </c>
+      <c r="F118">
+        <v>0.121</v>
+      </c>
+      <c r="G118">
+        <v>382.5</v>
+      </c>
+      <c r="H118">
+        <v>270</v>
+      </c>
+      <c r="I118">
+        <v>322</v>
+      </c>
+      <c r="J118">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>9792058</v>
+      </c>
+      <c r="B119" t="s">
+        <v>31</v>
+      </c>
+      <c r="C119">
+        <v>75</v>
+      </c>
+      <c r="D119">
+        <v>458</v>
+      </c>
+      <c r="E119">
+        <v>14.05</v>
+      </c>
+      <c r="F119">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="G119">
+        <v>400</v>
+      </c>
+      <c r="H119">
+        <v>288</v>
+      </c>
+      <c r="I119">
+        <v>288</v>
+      </c>
+      <c r="J119">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>9792058</v>
+      </c>
+      <c r="B120" t="s">
+        <v>31</v>
+      </c>
+      <c r="C120">
+        <v>100</v>
+      </c>
+      <c r="D120">
+        <v>610</v>
+      </c>
+      <c r="E120">
+        <v>17.28</v>
+      </c>
+      <c r="F120">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G120">
+        <v>432.5</v>
+      </c>
+      <c r="H120">
+        <v>333</v>
+      </c>
+      <c r="I120">
+        <v>307</v>
+      </c>
+      <c r="J120">
+        <v>23</v>
+      </c>
+      <c r="K120">
+        <v>197.4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>9792058</v>
+      </c>
+      <c r="B121" t="s">
+        <v>31</v>
+      </c>
+      <c r="C121">
+        <v>110</v>
+      </c>
+      <c r="D121">
+        <v>671</v>
+      </c>
+      <c r="E121">
+        <v>18.3</v>
+      </c>
+      <c r="F121">
+        <v>0.307</v>
+      </c>
+      <c r="G121">
+        <v>480</v>
+      </c>
+      <c r="H121">
+        <v>353</v>
+      </c>
+      <c r="I121">
+        <v>326</v>
+      </c>
+      <c r="J121">
+        <v>24.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E90832368BF3F64B8DDAA3DCE019ED58" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="233d7e41649bc1e193645dcf63c5b6cf">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="cdbaa21b-10dc-4fb4-9201-8770be8f96c9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="50b200f850c75d92ebc25be50ebd9f79" ns3:_="">
-    <xsd:import namespace="cdbaa21b-10dc-4fb4-9201-8770be8f96c9"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:_activity" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cdbaa21b-10dc-4fb4-9201-8770be8f96c9" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="12" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_activity" ma:index="13" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSystemTags" ma:index="14" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="cdbaa21b-10dc-4fb4-9201-8770be8f96c9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E9617E1-05F3-40E5-B27E-A2478E9BE2FA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6289BD57-4406-45F7-BB47-DD3BB5B441FA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="cdbaa21b-10dc-4fb4-9201-8770be8f96c9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1435314-7153-44CE-BFAE-AE559C36D7D0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="cdbaa21b-10dc-4fb4-9201-8770be8f96c9"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Aepms-backend/data/ae_shop_trial.xlsx
+++ b/Aepms-backend/data/ae_shop_trial.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOKUL\Desktop\Ozellar_project\Aepms-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C188E8-4336-4AE3-AB76-072E20534FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122295DF-F3D5-4409-8002-7FE696B0E2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="42">
   <si>
     <t>imo_number</t>
   </si>
@@ -2405,8 +2405,8 @@
       <c r="F32" s="3">
         <v>0.04</v>
       </c>
-      <c r="G32">
-        <v>208.5</v>
+      <c r="G32" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H32" s="3">
         <v>255.8</v>
@@ -2440,8 +2440,8 @@
       <c r="F33" s="3">
         <v>0.115</v>
       </c>
-      <c r="G33">
-        <v>459.5</v>
+      <c r="G33" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H33" s="3">
         <v>264.2</v>
@@ -2475,8 +2475,8 @@
       <c r="F34" s="3">
         <v>0.19500000000000001</v>
       </c>
-      <c r="G34">
-        <v>460.5</v>
+      <c r="G34" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H34" s="3">
         <v>278.3</v>
@@ -2510,8 +2510,8 @@
       <c r="F35" s="3">
         <v>0.28499999999999998</v>
       </c>
-      <c r="G35">
-        <v>495.8</v>
+      <c r="G35" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H35" s="3">
         <v>318.3</v>
@@ -2545,8 +2545,8 @@
       <c r="F36" s="3">
         <v>0.30499999999999999</v>
       </c>
-      <c r="G36">
-        <v>525</v>
+      <c r="G36" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H36" s="3">
         <v>331.7</v>
@@ -2580,8 +2580,8 @@
       <c r="F37" s="3">
         <v>0.04</v>
       </c>
-      <c r="G37">
-        <v>208.5</v>
+      <c r="G37" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H37" s="3">
         <v>260</v>
@@ -2615,8 +2615,8 @@
       <c r="F38" s="3">
         <v>0.11</v>
       </c>
-      <c r="G38">
-        <v>459.5</v>
+      <c r="G38" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H38" s="3">
         <v>273.3</v>
@@ -2650,8 +2650,8 @@
       <c r="F39" s="3">
         <v>0.19500000000000001</v>
       </c>
-      <c r="G39">
-        <v>460.5</v>
+      <c r="G39" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H39" s="3">
         <v>283.3</v>
@@ -2685,8 +2685,8 @@
       <c r="F40" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="G40">
-        <v>495.8</v>
+      <c r="G40" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H40" s="3">
         <v>323.3</v>
@@ -2720,8 +2720,8 @@
       <c r="F41" s="3">
         <v>0.31</v>
       </c>
-      <c r="G41">
-        <v>525</v>
+      <c r="G41" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H41" s="3">
         <v>336.7</v>
@@ -2755,8 +2755,8 @@
       <c r="F42" s="3">
         <v>0.04</v>
       </c>
-      <c r="G42">
-        <v>208.5</v>
+      <c r="G42" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H42" s="3">
         <v>256.7</v>
@@ -2790,8 +2790,8 @@
       <c r="F43" s="3">
         <v>0.115</v>
       </c>
-      <c r="G43">
-        <v>459.5</v>
+      <c r="G43" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H43" s="3">
         <v>271.7</v>
@@ -2825,8 +2825,8 @@
       <c r="F44" s="3">
         <v>0.2</v>
       </c>
-      <c r="G44">
-        <v>460.5</v>
+      <c r="G44" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H44" s="3">
         <v>283.3</v>
@@ -2860,8 +2860,8 @@
       <c r="F45" s="3">
         <v>0.3</v>
       </c>
-      <c r="G45">
-        <v>495.8</v>
+      <c r="G45" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H45" s="3">
         <v>320</v>
@@ -2895,8 +2895,8 @@
       <c r="F46" s="3">
         <v>0.31</v>
       </c>
-      <c r="G46">
-        <v>525</v>
+      <c r="G46" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H46" s="3">
         <v>335.8</v>
@@ -4505,8 +4505,8 @@
       <c r="F92">
         <v>0.04</v>
       </c>
-      <c r="G92">
-        <v>416.5</v>
+      <c r="G92" t="s">
+        <v>41</v>
       </c>
       <c r="H92">
         <v>247</v>
@@ -4537,8 +4537,8 @@
       <c r="F93">
         <v>0.12</v>
       </c>
-      <c r="G93">
-        <v>461.5</v>
+      <c r="G93" t="s">
+        <v>41</v>
       </c>
       <c r="H93">
         <v>258</v>
@@ -4569,8 +4569,8 @@
       <c r="F94">
         <v>0.19500000000000001</v>
       </c>
-      <c r="G94">
-        <v>471.5</v>
+      <c r="G94" t="s">
+        <v>41</v>
       </c>
       <c r="H94">
         <v>283</v>
@@ -4601,8 +4601,8 @@
       <c r="F95">
         <v>0.28000000000000003</v>
       </c>
-      <c r="G95">
-        <v>519.5</v>
+      <c r="G95" t="s">
+        <v>41</v>
       </c>
       <c r="H95">
         <v>308</v>
@@ -4636,8 +4636,8 @@
       <c r="F96">
         <v>0.31</v>
       </c>
-      <c r="G96">
-        <v>542</v>
+      <c r="G96" t="s">
+        <v>41</v>
       </c>
       <c r="H96">
         <v>328</v>
@@ -4668,8 +4668,8 @@
       <c r="F97">
         <v>0.04</v>
       </c>
-      <c r="G97">
-        <v>415</v>
+      <c r="G97" t="s">
+        <v>41</v>
       </c>
       <c r="H97">
         <v>260</v>
@@ -4700,8 +4700,8 @@
       <c r="F98">
         <v>0.115</v>
       </c>
-      <c r="G98">
-        <v>456</v>
+      <c r="G98" t="s">
+        <v>41</v>
       </c>
       <c r="H98">
         <v>264</v>
@@ -4732,8 +4732,8 @@
       <c r="F99">
         <v>0.19500000000000001</v>
       </c>
-      <c r="G99">
-        <v>461.5</v>
+      <c r="G99" t="s">
+        <v>41</v>
       </c>
       <c r="H99">
         <v>283</v>
@@ -4764,8 +4764,8 @@
       <c r="F100">
         <v>0.28000000000000003</v>
       </c>
-      <c r="G100">
-        <v>506.8</v>
+      <c r="G100" t="s">
+        <v>41</v>
       </c>
       <c r="H100">
         <v>318</v>
@@ -4799,8 +4799,8 @@
       <c r="F101">
         <v>0.28499999999999998</v>
       </c>
-      <c r="G101">
-        <v>536</v>
+      <c r="G101" t="s">
+        <v>41</v>
       </c>
       <c r="H101">
         <v>328</v>
@@ -4831,8 +4831,8 @@
       <c r="F102">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="G102">
-        <v>411.5</v>
+      <c r="G102" t="s">
+        <v>41</v>
       </c>
       <c r="H102">
         <v>248</v>
@@ -4863,8 +4863,8 @@
       <c r="F103">
         <v>0.115</v>
       </c>
-      <c r="G103">
-        <v>450</v>
+      <c r="G103" t="s">
+        <v>41</v>
       </c>
       <c r="H103">
         <v>263</v>
@@ -4895,8 +4895,8 @@
       <c r="F104">
         <v>0.19</v>
       </c>
-      <c r="G104">
-        <v>453.5</v>
+      <c r="G104" t="s">
+        <v>41</v>
       </c>
       <c r="H104">
         <v>283</v>
@@ -4927,8 +4927,8 @@
       <c r="F105">
         <v>0.28000000000000003</v>
       </c>
-      <c r="G105">
-        <v>504.8</v>
+      <c r="G105" t="s">
+        <v>41</v>
       </c>
       <c r="H105">
         <v>311</v>
@@ -4962,8 +4962,8 @@
       <c r="F106">
         <v>0.28000000000000003</v>
       </c>
-      <c r="G106">
-        <v>534.5</v>
+      <c r="G106" t="s">
+        <v>41</v>
       </c>
       <c r="H106">
         <v>328</v>
@@ -4994,14 +4994,14 @@
       <c r="F107">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="G107">
-        <v>220</v>
+      <c r="G107" t="s">
+        <v>41</v>
       </c>
       <c r="H107">
         <v>248</v>
       </c>
-      <c r="I107">
-        <v>336</v>
+      <c r="I107" t="s">
+        <v>41</v>
       </c>
       <c r="J107">
         <v>12</v>
@@ -5026,14 +5026,14 @@
       <c r="F108">
         <v>0.12</v>
       </c>
-      <c r="G108">
-        <v>382.5</v>
+      <c r="G108" t="s">
+        <v>41</v>
       </c>
       <c r="H108">
         <v>262</v>
       </c>
-      <c r="I108">
-        <v>332</v>
+      <c r="I108" t="s">
+        <v>41</v>
       </c>
       <c r="J108">
         <v>16</v>
@@ -5058,14 +5058,14 @@
       <c r="F109">
         <v>0.20499999999999999</v>
       </c>
-      <c r="G109">
-        <v>395</v>
+      <c r="G109" t="s">
+        <v>41</v>
       </c>
       <c r="H109">
         <v>283</v>
       </c>
-      <c r="I109">
-        <v>303</v>
+      <c r="I109" t="s">
+        <v>41</v>
       </c>
       <c r="J109">
         <v>20</v>
@@ -5090,14 +5090,14 @@
       <c r="F110">
         <v>0.28100000000000003</v>
       </c>
-      <c r="G110">
-        <v>437.5</v>
+      <c r="G110" t="s">
+        <v>41</v>
       </c>
       <c r="H110">
         <v>321</v>
       </c>
-      <c r="I110">
-        <v>318</v>
+      <c r="I110" t="s">
+        <v>41</v>
       </c>
       <c r="J110">
         <v>23.5</v>
@@ -5125,14 +5125,14 @@
       <c r="F111">
         <v>0.308</v>
       </c>
-      <c r="G111">
-        <v>487.5</v>
+      <c r="G111" t="s">
+        <v>41</v>
       </c>
       <c r="H111">
         <v>342</v>
       </c>
-      <c r="I111">
-        <v>333</v>
+      <c r="I111" t="s">
+        <v>41</v>
       </c>
       <c r="J111">
         <v>25</v>
@@ -5157,14 +5157,14 @@
       <c r="F112">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="G112">
-        <v>215</v>
+      <c r="G112" t="s">
+        <v>41</v>
       </c>
       <c r="H112">
         <v>250</v>
       </c>
-      <c r="I112">
-        <v>334</v>
+      <c r="I112" t="s">
+        <v>41</v>
       </c>
       <c r="J112">
         <v>11.5</v>
@@ -5189,14 +5189,14 @@
       <c r="F113">
         <v>0.12</v>
       </c>
-      <c r="G113">
-        <v>390</v>
+      <c r="G113" t="s">
+        <v>41</v>
       </c>
       <c r="H113">
         <v>267</v>
       </c>
-      <c r="I113">
-        <v>329</v>
+      <c r="I113" t="s">
+        <v>41</v>
       </c>
       <c r="J113">
         <v>16</v>
@@ -5221,14 +5221,14 @@
       <c r="F114">
         <v>0.20399999999999999</v>
       </c>
-      <c r="G114">
-        <v>400</v>
+      <c r="G114" t="s">
+        <v>41</v>
       </c>
       <c r="H114">
         <v>284</v>
       </c>
-      <c r="I114">
-        <v>297</v>
+      <c r="I114" t="s">
+        <v>41</v>
       </c>
       <c r="J114">
         <v>20</v>
@@ -5253,14 +5253,14 @@
       <c r="F115">
         <v>0.28199999999999997</v>
       </c>
-      <c r="G115">
-        <v>435</v>
+      <c r="G115" t="s">
+        <v>41</v>
       </c>
       <c r="H115">
         <v>324</v>
       </c>
-      <c r="I115">
-        <v>310.5</v>
+      <c r="I115" t="s">
+        <v>41</v>
       </c>
       <c r="J115">
         <v>23</v>
@@ -5288,14 +5288,14 @@
       <c r="F116">
         <v>0.30499999999999999</v>
       </c>
-      <c r="G116">
-        <v>487.5</v>
+      <c r="G116" t="s">
+        <v>41</v>
       </c>
       <c r="H116">
         <v>347</v>
       </c>
-      <c r="I116">
-        <v>328</v>
+      <c r="I116" t="s">
+        <v>41</v>
       </c>
       <c r="J116">
         <v>24.5</v>
@@ -5320,14 +5320,14 @@
       <c r="F117">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="G117">
-        <v>217.5</v>
+      <c r="G117" t="s">
+        <v>41</v>
       </c>
       <c r="H117">
         <v>253</v>
       </c>
-      <c r="I117">
-        <v>333</v>
+      <c r="I117" t="s">
+        <v>41</v>
       </c>
       <c r="J117">
         <v>11.5</v>
@@ -5352,14 +5352,14 @@
       <c r="F118">
         <v>0.121</v>
       </c>
-      <c r="G118">
-        <v>382.5</v>
+      <c r="G118" t="s">
+        <v>41</v>
       </c>
       <c r="H118">
         <v>270</v>
       </c>
-      <c r="I118">
-        <v>322</v>
+      <c r="I118" t="s">
+        <v>41</v>
       </c>
       <c r="J118">
         <v>16</v>
@@ -5384,14 +5384,14 @@
       <c r="F119">
         <v>0.20499999999999999</v>
       </c>
-      <c r="G119">
-        <v>400</v>
+      <c r="G119" t="s">
+        <v>41</v>
       </c>
       <c r="H119">
         <v>288</v>
       </c>
-      <c r="I119">
-        <v>288</v>
+      <c r="I119" t="s">
+        <v>41</v>
       </c>
       <c r="J119">
         <v>20</v>
@@ -5416,14 +5416,14 @@
       <c r="F120">
         <v>0.28000000000000003</v>
       </c>
-      <c r="G120">
-        <v>432.5</v>
+      <c r="G120" t="s">
+        <v>41</v>
       </c>
       <c r="H120">
         <v>333</v>
       </c>
-      <c r="I120">
-        <v>307</v>
+      <c r="I120" t="s">
+        <v>41</v>
       </c>
       <c r="J120">
         <v>23</v>
@@ -5451,14 +5451,14 @@
       <c r="F121">
         <v>0.307</v>
       </c>
-      <c r="G121">
-        <v>480</v>
+      <c r="G121" t="s">
+        <v>41</v>
       </c>
       <c r="H121">
         <v>353</v>
       </c>
-      <c r="I121">
-        <v>326</v>
+      <c r="I121" t="s">
+        <v>41</v>
       </c>
       <c r="J121">
         <v>24.5</v>

--- a/Aepms-backend/data/ae_shop_trial.xlsx
+++ b/Aepms-backend/data/ae_shop_trial.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOKUL\Desktop\Ozellar_project\Aepms-backend\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOKUL\Desktop\WORKPLACE\Workplace\Aepms-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122295DF-F3D5-4409-8002-7FE696B0E2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A389AF-6726-4A53-A5E7-821C3412C7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="58">
   <si>
     <t>imo_number</t>
   </si>
@@ -147,6 +147,54 @@
   </si>
   <si>
     <t>Not Available</t>
+  </si>
+  <si>
+    <t>DK520E0023</t>
+  </si>
+  <si>
+    <t>DK520E0024</t>
+  </si>
+  <si>
+    <t>DK520E0025</t>
+  </si>
+  <si>
+    <t>5DK-20e</t>
+  </si>
+  <si>
+    <t>DK520E0010</t>
+  </si>
+  <si>
+    <t>DK520E0011</t>
+  </si>
+  <si>
+    <t>DK520E0012</t>
+  </si>
+  <si>
+    <t>DK520Z2388</t>
+  </si>
+  <si>
+    <t>5DK-20</t>
+  </si>
+  <si>
+    <t>DK520Z2389</t>
+  </si>
+  <si>
+    <t>DK520Z2390</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>1762FXJ</t>
+  </si>
+  <si>
+    <t>6EY18AL</t>
+  </si>
+  <si>
+    <t>1763FXJ</t>
+  </si>
+  <si>
+    <t>1764FXJ</t>
   </si>
 </sst>
 </file>
@@ -612,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
@@ -1275,6 +1323,318 @@
         <v>900</v>
       </c>
     </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>9628910</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>770</v>
+      </c>
+      <c r="H26">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>9628910</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27">
+        <v>770</v>
+      </c>
+      <c r="H27">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>9628910</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28">
+        <v>770</v>
+      </c>
+      <c r="H28">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>9628893</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29">
+        <v>770</v>
+      </c>
+      <c r="H29">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>9628893</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30">
+        <v>770</v>
+      </c>
+      <c r="H30">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>9628893</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <v>770</v>
+      </c>
+      <c r="H31">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>9644500</v>
+      </c>
+      <c r="B32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" t="s">
+        <v>50</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32">
+        <v>463</v>
+      </c>
+      <c r="H32">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>9644500</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33">
+        <v>463</v>
+      </c>
+      <c r="H33">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>9644500</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34">
+        <v>463</v>
+      </c>
+      <c r="H34">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>9532082</v>
+      </c>
+      <c r="B35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" t="s">
+        <v>55</v>
+      </c>
+      <c r="F35">
+        <v>6</v>
+      </c>
+      <c r="G35">
+        <v>600</v>
+      </c>
+      <c r="H35">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>9532082</v>
+      </c>
+      <c r="B36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" t="s">
+        <v>55</v>
+      </c>
+      <c r="F36">
+        <v>6</v>
+      </c>
+      <c r="G36">
+        <v>600</v>
+      </c>
+      <c r="H36">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>9532082</v>
+      </c>
+      <c r="B37" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37">
+        <v>6</v>
+      </c>
+      <c r="G37">
+        <v>600</v>
+      </c>
+      <c r="H37">
+        <v>900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1286,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K181"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13.33203125" customWidth="1"/>
@@ -5464,6 +5824,2106 @@
         <v>24.5</v>
       </c>
     </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>9628910</v>
+      </c>
+      <c r="B122" t="s">
+        <v>42</v>
+      </c>
+      <c r="C122">
+        <v>25</v>
+      </c>
+      <c r="D122">
+        <v>180</v>
+      </c>
+      <c r="E122">
+        <v>6.34</v>
+      </c>
+      <c r="F122">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="G122">
+        <v>370</v>
+      </c>
+      <c r="H122">
+        <v>266</v>
+      </c>
+      <c r="I122">
+        <v>295</v>
+      </c>
+      <c r="J122">
+        <v>12</v>
+      </c>
+      <c r="K122">
+        <v>279.39999999999998</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>9628910</v>
+      </c>
+      <c r="B123" t="s">
+        <v>42</v>
+      </c>
+      <c r="C123">
+        <v>50</v>
+      </c>
+      <c r="D123">
+        <v>360</v>
+      </c>
+      <c r="E123">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="F123">
+        <v>0.123</v>
+      </c>
+      <c r="G123">
+        <v>395</v>
+      </c>
+      <c r="H123">
+        <v>273</v>
+      </c>
+      <c r="I123">
+        <v>295</v>
+      </c>
+      <c r="J123">
+        <v>16.5</v>
+      </c>
+      <c r="K123">
+        <v>220.8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>9628910</v>
+      </c>
+      <c r="B124" t="s">
+        <v>42</v>
+      </c>
+      <c r="C124">
+        <v>75</v>
+      </c>
+      <c r="D124">
+        <v>540</v>
+      </c>
+      <c r="E124">
+        <v>13.16</v>
+      </c>
+      <c r="F124">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="G124">
+        <v>420</v>
+      </c>
+      <c r="H124">
+        <v>295</v>
+      </c>
+      <c r="I124">
+        <v>285</v>
+      </c>
+      <c r="J124">
+        <v>19.5</v>
+      </c>
+      <c r="K124">
+        <v>209.7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>9628910</v>
+      </c>
+      <c r="B125" t="s">
+        <v>42</v>
+      </c>
+      <c r="C125">
+        <v>100</v>
+      </c>
+      <c r="D125">
+        <v>720</v>
+      </c>
+      <c r="E125">
+        <v>15.62</v>
+      </c>
+      <c r="F125">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="G125">
+        <v>470</v>
+      </c>
+      <c r="H125">
+        <v>343</v>
+      </c>
+      <c r="I125">
+        <v>295</v>
+      </c>
+      <c r="J125">
+        <v>23</v>
+      </c>
+      <c r="K125">
+        <v>208.7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>9628910</v>
+      </c>
+      <c r="B126" t="s">
+        <v>42</v>
+      </c>
+      <c r="C126">
+        <v>110</v>
+      </c>
+      <c r="D126">
+        <v>792</v>
+      </c>
+      <c r="E126">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="F126">
+        <v>0.315</v>
+      </c>
+      <c r="G126">
+        <v>495</v>
+      </c>
+      <c r="H126">
+        <v>366</v>
+      </c>
+      <c r="I126">
+        <v>300</v>
+      </c>
+      <c r="J126">
+        <v>24.5</v>
+      </c>
+      <c r="K126">
+        <v>206.1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>9628910</v>
+      </c>
+      <c r="B127" t="s">
+        <v>43</v>
+      </c>
+      <c r="C127">
+        <v>25</v>
+      </c>
+      <c r="D127">
+        <v>180</v>
+      </c>
+      <c r="E127">
+        <v>6.32</v>
+      </c>
+      <c r="F127">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G127">
+        <v>370</v>
+      </c>
+      <c r="H127">
+        <v>273</v>
+      </c>
+      <c r="I127">
+        <v>305</v>
+      </c>
+      <c r="J127">
+        <v>12</v>
+      </c>
+      <c r="K127">
+        <v>278.7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>9628910</v>
+      </c>
+      <c r="B128" t="s">
+        <v>43</v>
+      </c>
+      <c r="C128">
+        <v>50</v>
+      </c>
+      <c r="D128">
+        <v>360</v>
+      </c>
+      <c r="E128">
+        <v>9.92</v>
+      </c>
+      <c r="F128">
+        <v>0.12</v>
+      </c>
+      <c r="G128">
+        <v>395</v>
+      </c>
+      <c r="H128">
+        <v>277</v>
+      </c>
+      <c r="I128">
+        <v>300</v>
+      </c>
+      <c r="J128">
+        <v>16</v>
+      </c>
+      <c r="K128">
+        <v>220.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>9628910</v>
+      </c>
+      <c r="B129" t="s">
+        <v>43</v>
+      </c>
+      <c r="C129">
+        <v>75</v>
+      </c>
+      <c r="D129">
+        <v>540</v>
+      </c>
+      <c r="E129">
+        <v>13.16</v>
+      </c>
+      <c r="F129">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="G129">
+        <v>425</v>
+      </c>
+      <c r="H129">
+        <v>301</v>
+      </c>
+      <c r="I129">
+        <v>290</v>
+      </c>
+      <c r="J129">
+        <v>19.5</v>
+      </c>
+      <c r="K129">
+        <v>209.2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>9628910</v>
+      </c>
+      <c r="B130" t="s">
+        <v>43</v>
+      </c>
+      <c r="C130">
+        <v>100</v>
+      </c>
+      <c r="D130">
+        <v>720</v>
+      </c>
+      <c r="E130">
+        <v>15.66</v>
+      </c>
+      <c r="F130">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="G130">
+        <v>475</v>
+      </c>
+      <c r="H130">
+        <v>344</v>
+      </c>
+      <c r="I130">
+        <v>295</v>
+      </c>
+      <c r="J130">
+        <v>23.5</v>
+      </c>
+      <c r="K130">
+        <v>208.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>9628910</v>
+      </c>
+      <c r="B131" t="s">
+        <v>43</v>
+      </c>
+      <c r="C131">
+        <v>110</v>
+      </c>
+      <c r="D131">
+        <v>792</v>
+      </c>
+      <c r="E131">
+        <v>16.66</v>
+      </c>
+      <c r="F131">
+        <v>0.313</v>
+      </c>
+      <c r="G131">
+        <v>495</v>
+      </c>
+      <c r="H131">
+        <v>368</v>
+      </c>
+      <c r="I131">
+        <v>315</v>
+      </c>
+      <c r="J131">
+        <v>25</v>
+      </c>
+      <c r="K131">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>9628910</v>
+      </c>
+      <c r="B132" t="s">
+        <v>44</v>
+      </c>
+      <c r="C132">
+        <v>25</v>
+      </c>
+      <c r="D132">
+        <v>180</v>
+      </c>
+      <c r="E132">
+        <v>6.36</v>
+      </c>
+      <c r="F132">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="G132">
+        <v>360</v>
+      </c>
+      <c r="H132">
+        <v>275</v>
+      </c>
+      <c r="I132">
+        <v>285</v>
+      </c>
+      <c r="J132">
+        <v>12.5</v>
+      </c>
+      <c r="K132">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>9628910</v>
+      </c>
+      <c r="B133" t="s">
+        <v>44</v>
+      </c>
+      <c r="C133">
+        <v>50</v>
+      </c>
+      <c r="D133">
+        <v>360</v>
+      </c>
+      <c r="E133">
+        <v>9.92</v>
+      </c>
+      <c r="F133">
+        <v>0.12</v>
+      </c>
+      <c r="G133">
+        <v>390</v>
+      </c>
+      <c r="H133">
+        <v>277</v>
+      </c>
+      <c r="I133">
+        <v>300</v>
+      </c>
+      <c r="J133">
+        <v>16</v>
+      </c>
+      <c r="K133">
+        <v>220.2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>9628910</v>
+      </c>
+      <c r="B134" t="s">
+        <v>44</v>
+      </c>
+      <c r="C134">
+        <v>75</v>
+      </c>
+      <c r="D134">
+        <v>540</v>
+      </c>
+      <c r="E134">
+        <v>13.06</v>
+      </c>
+      <c r="F134">
+        <v>0.21</v>
+      </c>
+      <c r="G134">
+        <v>420</v>
+      </c>
+      <c r="H134">
+        <v>305</v>
+      </c>
+      <c r="I134">
+        <v>295</v>
+      </c>
+      <c r="J134">
+        <v>20</v>
+      </c>
+      <c r="K134">
+        <v>210.4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>9628910</v>
+      </c>
+      <c r="B135" t="s">
+        <v>44</v>
+      </c>
+      <c r="C135">
+        <v>100</v>
+      </c>
+      <c r="D135">
+        <v>720</v>
+      </c>
+      <c r="E135">
+        <v>15.62</v>
+      </c>
+      <c r="F135">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="G135">
+        <v>470</v>
+      </c>
+      <c r="H135">
+        <v>349</v>
+      </c>
+      <c r="I135">
+        <v>305</v>
+      </c>
+      <c r="J135">
+        <v>23.5</v>
+      </c>
+      <c r="K135">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>9628910</v>
+      </c>
+      <c r="B136" t="s">
+        <v>44</v>
+      </c>
+      <c r="C136">
+        <v>110</v>
+      </c>
+      <c r="D136">
+        <v>792</v>
+      </c>
+      <c r="E136">
+        <v>16.64</v>
+      </c>
+      <c r="F136">
+        <v>0.315</v>
+      </c>
+      <c r="G136">
+        <v>490</v>
+      </c>
+      <c r="H136">
+        <v>367</v>
+      </c>
+      <c r="I136">
+        <v>310</v>
+      </c>
+      <c r="J136">
+        <v>25</v>
+      </c>
+      <c r="K136">
+        <v>205.1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>9628893</v>
+      </c>
+      <c r="B137" t="s">
+        <v>46</v>
+      </c>
+      <c r="C137">
+        <v>25</v>
+      </c>
+      <c r="D137">
+        <v>180</v>
+      </c>
+      <c r="E137">
+        <v>6.76</v>
+      </c>
+      <c r="F137">
+        <v>0.04</v>
+      </c>
+      <c r="G137">
+        <v>350</v>
+      </c>
+      <c r="H137">
+        <v>269</v>
+      </c>
+      <c r="I137">
+        <v>300</v>
+      </c>
+      <c r="J137">
+        <v>12</v>
+      </c>
+      <c r="K137">
+        <v>276.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>9628893</v>
+      </c>
+      <c r="B138" t="s">
+        <v>46</v>
+      </c>
+      <c r="C138">
+        <v>50</v>
+      </c>
+      <c r="D138">
+        <v>360</v>
+      </c>
+      <c r="E138">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="F138">
+        <v>0.125</v>
+      </c>
+      <c r="G138">
+        <v>375</v>
+      </c>
+      <c r="H138">
+        <v>270</v>
+      </c>
+      <c r="I138">
+        <v>280</v>
+      </c>
+      <c r="J138">
+        <v>16</v>
+      </c>
+      <c r="K138">
+        <v>223.3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>9628893</v>
+      </c>
+      <c r="B139" t="s">
+        <v>46</v>
+      </c>
+      <c r="C139">
+        <v>75</v>
+      </c>
+      <c r="D139">
+        <v>540</v>
+      </c>
+      <c r="E139">
+        <v>12.94</v>
+      </c>
+      <c r="F139">
+        <v>0.21</v>
+      </c>
+      <c r="G139">
+        <v>415</v>
+      </c>
+      <c r="H139">
+        <v>302</v>
+      </c>
+      <c r="I139">
+        <v>270</v>
+      </c>
+      <c r="J139">
+        <v>20</v>
+      </c>
+      <c r="K139">
+        <v>213.4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>9628893</v>
+      </c>
+      <c r="B140" t="s">
+        <v>46</v>
+      </c>
+      <c r="C140">
+        <v>100</v>
+      </c>
+      <c r="D140">
+        <v>720</v>
+      </c>
+      <c r="E140">
+        <v>15.78</v>
+      </c>
+      <c r="F140">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="G140">
+        <v>460</v>
+      </c>
+      <c r="H140">
+        <v>349</v>
+      </c>
+      <c r="I140">
+        <v>280</v>
+      </c>
+      <c r="J140">
+        <v>23.5</v>
+      </c>
+      <c r="K140">
+        <v>211.6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>9628893</v>
+      </c>
+      <c r="B141" t="s">
+        <v>46</v>
+      </c>
+      <c r="C141">
+        <v>110</v>
+      </c>
+      <c r="D141">
+        <v>792</v>
+      </c>
+      <c r="E141">
+        <v>16.760000000000002</v>
+      </c>
+      <c r="F141">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="G141">
+        <v>480</v>
+      </c>
+      <c r="H141">
+        <v>370</v>
+      </c>
+      <c r="I141">
+        <v>300</v>
+      </c>
+      <c r="J141">
+        <v>25</v>
+      </c>
+      <c r="K141">
+        <v>210.8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>9628893</v>
+      </c>
+      <c r="B142" t="s">
+        <v>47</v>
+      </c>
+      <c r="C142">
+        <v>25</v>
+      </c>
+      <c r="D142">
+        <v>180</v>
+      </c>
+      <c r="E142">
+        <v>6.72</v>
+      </c>
+      <c r="F142">
+        <v>0.04</v>
+      </c>
+      <c r="G142">
+        <v>360</v>
+      </c>
+      <c r="H142">
+        <v>272</v>
+      </c>
+      <c r="I142">
+        <v>305</v>
+      </c>
+      <c r="J142">
+        <v>11.5</v>
+      </c>
+      <c r="K142">
+        <v>276.10000000000002</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>9628893</v>
+      </c>
+      <c r="B143" t="s">
+        <v>47</v>
+      </c>
+      <c r="C143">
+        <v>50</v>
+      </c>
+      <c r="D143">
+        <v>360</v>
+      </c>
+      <c r="E143">
+        <v>10.02</v>
+      </c>
+      <c r="F143">
+        <v>0.12</v>
+      </c>
+      <c r="G143">
+        <v>375</v>
+      </c>
+      <c r="H143">
+        <v>272</v>
+      </c>
+      <c r="I143">
+        <v>290</v>
+      </c>
+      <c r="J143">
+        <v>16</v>
+      </c>
+      <c r="K143">
+        <v>222.8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>9628893</v>
+      </c>
+      <c r="B144" t="s">
+        <v>47</v>
+      </c>
+      <c r="C144">
+        <v>75</v>
+      </c>
+      <c r="D144">
+        <v>540</v>
+      </c>
+      <c r="E144">
+        <v>12.94</v>
+      </c>
+      <c r="F144">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="G144">
+        <v>415</v>
+      </c>
+      <c r="H144">
+        <v>302</v>
+      </c>
+      <c r="I144">
+        <v>275</v>
+      </c>
+      <c r="J144">
+        <v>20</v>
+      </c>
+      <c r="K144">
+        <v>212.9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>9628893</v>
+      </c>
+      <c r="B145" t="s">
+        <v>47</v>
+      </c>
+      <c r="C145">
+        <v>100</v>
+      </c>
+      <c r="D145">
+        <v>720</v>
+      </c>
+      <c r="E145">
+        <v>15.88</v>
+      </c>
+      <c r="F145">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="G145">
+        <v>460</v>
+      </c>
+      <c r="H145">
+        <v>351</v>
+      </c>
+      <c r="I145">
+        <v>295</v>
+      </c>
+      <c r="J145">
+        <v>23.5</v>
+      </c>
+      <c r="K145">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>9628893</v>
+      </c>
+      <c r="B146" t="s">
+        <v>47</v>
+      </c>
+      <c r="C146">
+        <v>110</v>
+      </c>
+      <c r="D146">
+        <v>792</v>
+      </c>
+      <c r="E146">
+        <v>16.760000000000002</v>
+      </c>
+      <c r="F146">
+        <v>0.32</v>
+      </c>
+      <c r="G146">
+        <v>485</v>
+      </c>
+      <c r="H146">
+        <v>375</v>
+      </c>
+      <c r="I146">
+        <v>310</v>
+      </c>
+      <c r="J146">
+        <v>25</v>
+      </c>
+      <c r="K146">
+        <v>210.2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>9628893</v>
+      </c>
+      <c r="B147" t="s">
+        <v>48</v>
+      </c>
+      <c r="C147">
+        <v>25</v>
+      </c>
+      <c r="D147">
+        <v>180</v>
+      </c>
+      <c r="E147">
+        <v>6.78</v>
+      </c>
+      <c r="F147">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="G147">
+        <v>350</v>
+      </c>
+      <c r="H147">
+        <v>264</v>
+      </c>
+      <c r="I147">
+        <v>295</v>
+      </c>
+      <c r="J147">
+        <v>11.5</v>
+      </c>
+      <c r="K147">
+        <v>277.89999999999998</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>9628893</v>
+      </c>
+      <c r="B148" t="s">
+        <v>48</v>
+      </c>
+      <c r="C148">
+        <v>50</v>
+      </c>
+      <c r="D148">
+        <v>360</v>
+      </c>
+      <c r="E148">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="F148">
+        <v>0.125</v>
+      </c>
+      <c r="G148">
+        <v>365</v>
+      </c>
+      <c r="H148">
+        <v>270</v>
+      </c>
+      <c r="I148">
+        <v>280</v>
+      </c>
+      <c r="J148">
+        <v>16</v>
+      </c>
+      <c r="K148">
+        <v>223.3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>9628893</v>
+      </c>
+      <c r="B149" t="s">
+        <v>48</v>
+      </c>
+      <c r="C149">
+        <v>75</v>
+      </c>
+      <c r="D149">
+        <v>540</v>
+      </c>
+      <c r="E149">
+        <v>13</v>
+      </c>
+      <c r="F149">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="G149">
+        <v>410</v>
+      </c>
+      <c r="H149">
+        <v>305</v>
+      </c>
+      <c r="I149">
+        <v>275</v>
+      </c>
+      <c r="J149">
+        <v>20</v>
+      </c>
+      <c r="K149">
+        <v>213.4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>9628893</v>
+      </c>
+      <c r="B150" t="s">
+        <v>48</v>
+      </c>
+      <c r="C150">
+        <v>100</v>
+      </c>
+      <c r="D150">
+        <v>720</v>
+      </c>
+      <c r="E150">
+        <v>15.82</v>
+      </c>
+      <c r="F150">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="G150">
+        <v>460</v>
+      </c>
+      <c r="H150">
+        <v>351</v>
+      </c>
+      <c r="I150">
+        <v>290</v>
+      </c>
+      <c r="J150">
+        <v>23</v>
+      </c>
+      <c r="K150">
+        <v>211.9</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>9628893</v>
+      </c>
+      <c r="B151" t="s">
+        <v>48</v>
+      </c>
+      <c r="C151">
+        <v>110</v>
+      </c>
+      <c r="D151">
+        <v>792</v>
+      </c>
+      <c r="E151">
+        <v>16.739999999999998</v>
+      </c>
+      <c r="F151">
+        <v>0.32</v>
+      </c>
+      <c r="G151">
+        <v>485</v>
+      </c>
+      <c r="H151">
+        <v>379</v>
+      </c>
+      <c r="I151">
+        <v>310</v>
+      </c>
+      <c r="J151">
+        <v>25</v>
+      </c>
+      <c r="K151">
+        <v>210.4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>9644500</v>
+      </c>
+      <c r="B152" t="s">
+        <v>49</v>
+      </c>
+      <c r="C152">
+        <v>25</v>
+      </c>
+      <c r="D152">
+        <v>105</v>
+      </c>
+      <c r="E152">
+        <v>5.52</v>
+      </c>
+      <c r="F152">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G152" t="s">
+        <v>53</v>
+      </c>
+      <c r="H152">
+        <v>275</v>
+      </c>
+      <c r="I152">
+        <v>250</v>
+      </c>
+      <c r="J152">
+        <v>12</v>
+      </c>
+      <c r="K152">
+        <v>315.60000000000002</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>9644500</v>
+      </c>
+      <c r="B153" t="s">
+        <v>49</v>
+      </c>
+      <c r="C153">
+        <v>50</v>
+      </c>
+      <c r="D153">
+        <v>210</v>
+      </c>
+      <c r="E153">
+        <v>7</v>
+      </c>
+      <c r="F153">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="G153" t="s">
+        <v>53</v>
+      </c>
+      <c r="H153">
+        <v>334</v>
+      </c>
+      <c r="I153">
+        <v>320</v>
+      </c>
+      <c r="J153">
+        <v>15</v>
+      </c>
+      <c r="K153">
+        <v>240.8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>9644500</v>
+      </c>
+      <c r="B154" t="s">
+        <v>49</v>
+      </c>
+      <c r="C154">
+        <v>75</v>
+      </c>
+      <c r="D154">
+        <v>315</v>
+      </c>
+      <c r="E154">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="F154">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="G154" t="s">
+        <v>53</v>
+      </c>
+      <c r="H154">
+        <v>354</v>
+      </c>
+      <c r="I154">
+        <v>350</v>
+      </c>
+      <c r="J154">
+        <v>18</v>
+      </c>
+      <c r="K154">
+        <v>218.6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>9644500</v>
+      </c>
+      <c r="B155" t="s">
+        <v>49</v>
+      </c>
+      <c r="C155">
+        <v>100</v>
+      </c>
+      <c r="D155">
+        <v>420</v>
+      </c>
+      <c r="E155">
+        <v>10.94</v>
+      </c>
+      <c r="F155">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G155" t="s">
+        <v>53</v>
+      </c>
+      <c r="H155">
+        <v>374</v>
+      </c>
+      <c r="I155">
+        <v>350</v>
+      </c>
+      <c r="J155">
+        <v>21</v>
+      </c>
+      <c r="K155">
+        <v>209.1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>9644500</v>
+      </c>
+      <c r="B156" t="s">
+        <v>49</v>
+      </c>
+      <c r="C156">
+        <v>110</v>
+      </c>
+      <c r="D156">
+        <v>460</v>
+      </c>
+      <c r="E156">
+        <v>11.72</v>
+      </c>
+      <c r="F156">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="G156" t="s">
+        <v>53</v>
+      </c>
+      <c r="H156">
+        <v>391</v>
+      </c>
+      <c r="I156">
+        <v>360</v>
+      </c>
+      <c r="J156">
+        <v>22</v>
+      </c>
+      <c r="K156">
+        <v>207.3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>9644500</v>
+      </c>
+      <c r="B157" t="s">
+        <v>51</v>
+      </c>
+      <c r="C157">
+        <v>25</v>
+      </c>
+      <c r="D157">
+        <v>105</v>
+      </c>
+      <c r="E157">
+        <v>5.46</v>
+      </c>
+      <c r="F157">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G157" t="s">
+        <v>53</v>
+      </c>
+      <c r="H157">
+        <v>263</v>
+      </c>
+      <c r="I157">
+        <v>250</v>
+      </c>
+      <c r="J157">
+        <v>11.5</v>
+      </c>
+      <c r="K157">
+        <v>315.39999999999998</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>9644500</v>
+      </c>
+      <c r="B158" t="s">
+        <v>51</v>
+      </c>
+      <c r="C158">
+        <v>50</v>
+      </c>
+      <c r="D158">
+        <v>210</v>
+      </c>
+      <c r="E158">
+        <v>6.96</v>
+      </c>
+      <c r="F158">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="G158" t="s">
+        <v>53</v>
+      </c>
+      <c r="H158">
+        <v>325</v>
+      </c>
+      <c r="I158">
+        <v>320</v>
+      </c>
+      <c r="J158">
+        <v>15</v>
+      </c>
+      <c r="K158">
+        <v>240.1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>9644500</v>
+      </c>
+      <c r="B159" t="s">
+        <v>51</v>
+      </c>
+      <c r="C159">
+        <v>75</v>
+      </c>
+      <c r="D159">
+        <v>315</v>
+      </c>
+      <c r="E159">
+        <v>8.98</v>
+      </c>
+      <c r="F159">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="G159" t="s">
+        <v>53</v>
+      </c>
+      <c r="H159">
+        <v>348</v>
+      </c>
+      <c r="I159">
+        <v>350</v>
+      </c>
+      <c r="J159">
+        <v>18</v>
+      </c>
+      <c r="K159">
+        <v>217.9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>9644500</v>
+      </c>
+      <c r="B160" t="s">
+        <v>51</v>
+      </c>
+      <c r="C160">
+        <v>100</v>
+      </c>
+      <c r="D160">
+        <v>420</v>
+      </c>
+      <c r="E160">
+        <v>11.04</v>
+      </c>
+      <c r="F160">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="G160" t="s">
+        <v>53</v>
+      </c>
+      <c r="H160">
+        <v>361</v>
+      </c>
+      <c r="I160">
+        <v>340</v>
+      </c>
+      <c r="J160">
+        <v>21</v>
+      </c>
+      <c r="K160">
+        <v>208.8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>9644500</v>
+      </c>
+      <c r="B161" t="s">
+        <v>51</v>
+      </c>
+      <c r="C161">
+        <v>110</v>
+      </c>
+      <c r="D161">
+        <v>460</v>
+      </c>
+      <c r="E161">
+        <v>11.92</v>
+      </c>
+      <c r="F161">
+        <v>0.151</v>
+      </c>
+      <c r="G161" t="s">
+        <v>53</v>
+      </c>
+      <c r="H161">
+        <v>375</v>
+      </c>
+      <c r="I161">
+        <v>345</v>
+      </c>
+      <c r="J161">
+        <v>22.5</v>
+      </c>
+      <c r="K161">
+        <v>207.1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>9644500</v>
+      </c>
+      <c r="B162" t="s">
+        <v>52</v>
+      </c>
+      <c r="C162">
+        <v>25</v>
+      </c>
+      <c r="D162">
+        <v>105</v>
+      </c>
+      <c r="E162">
+        <v>5.48</v>
+      </c>
+      <c r="F162">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="G162" t="s">
+        <v>53</v>
+      </c>
+      <c r="H162">
+        <v>273</v>
+      </c>
+      <c r="I162">
+        <v>270</v>
+      </c>
+      <c r="J162">
+        <v>12</v>
+      </c>
+      <c r="K162">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <v>9644500</v>
+      </c>
+      <c r="B163" t="s">
+        <v>52</v>
+      </c>
+      <c r="C163">
+        <v>50</v>
+      </c>
+      <c r="D163">
+        <v>210</v>
+      </c>
+      <c r="E163">
+        <v>6.96</v>
+      </c>
+      <c r="F163">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="G163" t="s">
+        <v>53</v>
+      </c>
+      <c r="H163">
+        <v>338</v>
+      </c>
+      <c r="I163">
+        <v>330</v>
+      </c>
+      <c r="J163">
+        <v>15</v>
+      </c>
+      <c r="K163">
+        <v>240.4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>9644500</v>
+      </c>
+      <c r="B164" t="s">
+        <v>52</v>
+      </c>
+      <c r="C164">
+        <v>75</v>
+      </c>
+      <c r="D164">
+        <v>315</v>
+      </c>
+      <c r="E164">
+        <v>8.92</v>
+      </c>
+      <c r="F164">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="G164" t="s">
+        <v>53</v>
+      </c>
+      <c r="H164">
+        <v>352</v>
+      </c>
+      <c r="I164">
+        <v>340</v>
+      </c>
+      <c r="J164">
+        <v>18</v>
+      </c>
+      <c r="K164">
+        <v>218.2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>9644500</v>
+      </c>
+      <c r="B165" t="s">
+        <v>52</v>
+      </c>
+      <c r="C165">
+        <v>100</v>
+      </c>
+      <c r="D165">
+        <v>420</v>
+      </c>
+      <c r="E165">
+        <v>10.98</v>
+      </c>
+      <c r="F165">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="G165" t="s">
+        <v>53</v>
+      </c>
+      <c r="H165">
+        <v>370</v>
+      </c>
+      <c r="I165">
+        <v>340</v>
+      </c>
+      <c r="J165">
+        <v>21</v>
+      </c>
+      <c r="K165">
+        <v>209.1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>9644500</v>
+      </c>
+      <c r="B166" t="s">
+        <v>52</v>
+      </c>
+      <c r="C166">
+        <v>110</v>
+      </c>
+      <c r="D166">
+        <v>460</v>
+      </c>
+      <c r="E166">
+        <v>11.88</v>
+      </c>
+      <c r="F166">
+        <v>0.15</v>
+      </c>
+      <c r="G166" t="s">
+        <v>53</v>
+      </c>
+      <c r="H166">
+        <v>382</v>
+      </c>
+      <c r="I166">
+        <v>335</v>
+      </c>
+      <c r="J166">
+        <v>22.5</v>
+      </c>
+      <c r="K166">
+        <v>207.7</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>9532082</v>
+      </c>
+      <c r="B167" t="s">
+        <v>54</v>
+      </c>
+      <c r="C167">
+        <v>25</v>
+      </c>
+      <c r="D167">
+        <v>150</v>
+      </c>
+      <c r="E167">
+        <v>7.1</v>
+      </c>
+      <c r="F167">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G167">
+        <v>355</v>
+      </c>
+      <c r="H167">
+        <v>273</v>
+      </c>
+      <c r="I167">
+        <v>315</v>
+      </c>
+      <c r="J167">
+        <v>29</v>
+      </c>
+      <c r="K167">
+        <v>257.23</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>9532082</v>
+      </c>
+      <c r="B168" t="s">
+        <v>54</v>
+      </c>
+      <c r="C168">
+        <v>50</v>
+      </c>
+      <c r="D168">
+        <v>300</v>
+      </c>
+      <c r="E168">
+        <v>10.1</v>
+      </c>
+      <c r="F168">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="G168">
+        <v>425</v>
+      </c>
+      <c r="H168">
+        <v>315</v>
+      </c>
+      <c r="I168">
+        <v>340</v>
+      </c>
+      <c r="J168">
+        <v>32</v>
+      </c>
+      <c r="K168">
+        <v>218.87</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>9532082</v>
+      </c>
+      <c r="B169" t="s">
+        <v>54</v>
+      </c>
+      <c r="C169">
+        <v>75</v>
+      </c>
+      <c r="D169">
+        <v>450</v>
+      </c>
+      <c r="E169">
+        <v>13.4</v>
+      </c>
+      <c r="F169">
+        <v>0.151</v>
+      </c>
+      <c r="G169">
+        <v>450</v>
+      </c>
+      <c r="H169">
+        <v>328</v>
+      </c>
+      <c r="I169">
+        <v>320</v>
+      </c>
+      <c r="J169">
+        <v>41</v>
+      </c>
+      <c r="K169">
+        <v>207.76</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>9532082</v>
+      </c>
+      <c r="B170" t="s">
+        <v>54</v>
+      </c>
+      <c r="C170">
+        <v>100</v>
+      </c>
+      <c r="D170">
+        <v>600</v>
+      </c>
+      <c r="E170">
+        <v>16</v>
+      </c>
+      <c r="F170">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="G170">
+        <v>482.5</v>
+      </c>
+      <c r="H170">
+        <v>358</v>
+      </c>
+      <c r="I170">
+        <v>315</v>
+      </c>
+      <c r="J170">
+        <v>50</v>
+      </c>
+      <c r="K170">
+        <v>204.66</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>9532082</v>
+      </c>
+      <c r="B171" t="s">
+        <v>54</v>
+      </c>
+      <c r="C171">
+        <v>110</v>
+      </c>
+      <c r="D171">
+        <v>660</v>
+      </c>
+      <c r="E171">
+        <v>17</v>
+      </c>
+      <c r="F171">
+        <v>0.253</v>
+      </c>
+      <c r="G171">
+        <v>500</v>
+      </c>
+      <c r="H171">
+        <v>373</v>
+      </c>
+      <c r="I171">
+        <v>320</v>
+      </c>
+      <c r="J171">
+        <v>53</v>
+      </c>
+      <c r="K171">
+        <v>204.88</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>9532082</v>
+      </c>
+      <c r="B172" t="s">
+        <v>56</v>
+      </c>
+      <c r="C172">
+        <v>25</v>
+      </c>
+      <c r="D172">
+        <v>150</v>
+      </c>
+      <c r="E172">
+        <v>7.1</v>
+      </c>
+      <c r="F172">
+        <v>2.7E-2</v>
+      </c>
+      <c r="G172">
+        <v>360</v>
+      </c>
+      <c r="H172">
+        <v>280</v>
+      </c>
+      <c r="I172">
+        <v>320</v>
+      </c>
+      <c r="J172">
+        <v>29</v>
+      </c>
+      <c r="K172">
+        <v>257.51</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>9532082</v>
+      </c>
+      <c r="B173" t="s">
+        <v>56</v>
+      </c>
+      <c r="C173">
+        <v>50</v>
+      </c>
+      <c r="D173">
+        <v>300</v>
+      </c>
+      <c r="E173">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F173">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="G173">
+        <v>435</v>
+      </c>
+      <c r="H173">
+        <v>322</v>
+      </c>
+      <c r="I173">
+        <v>340</v>
+      </c>
+      <c r="J173">
+        <v>34</v>
+      </c>
+      <c r="K173">
+        <v>218.6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>9532082</v>
+      </c>
+      <c r="B174" t="s">
+        <v>56</v>
+      </c>
+      <c r="C174">
+        <v>75</v>
+      </c>
+      <c r="D174">
+        <v>450</v>
+      </c>
+      <c r="E174">
+        <v>13.3</v>
+      </c>
+      <c r="F174">
+        <v>0.152</v>
+      </c>
+      <c r="G174">
+        <v>447.5</v>
+      </c>
+      <c r="H174">
+        <v>332</v>
+      </c>
+      <c r="I174">
+        <v>325</v>
+      </c>
+      <c r="J174">
+        <v>41</v>
+      </c>
+      <c r="K174">
+        <v>208.03</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>9532082</v>
+      </c>
+      <c r="B175" t="s">
+        <v>56</v>
+      </c>
+      <c r="C175">
+        <v>100</v>
+      </c>
+      <c r="D175">
+        <v>600</v>
+      </c>
+      <c r="E175">
+        <v>16</v>
+      </c>
+      <c r="F175">
+        <v>0.223</v>
+      </c>
+      <c r="G175">
+        <v>485</v>
+      </c>
+      <c r="H175">
+        <v>359</v>
+      </c>
+      <c r="I175">
+        <v>325</v>
+      </c>
+      <c r="J175">
+        <v>50</v>
+      </c>
+      <c r="K175">
+        <v>204.94</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>9532082</v>
+      </c>
+      <c r="B176" t="s">
+        <v>56</v>
+      </c>
+      <c r="C176">
+        <v>110</v>
+      </c>
+      <c r="D176">
+        <v>660</v>
+      </c>
+      <c r="E176">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="F176">
+        <v>0.253</v>
+      </c>
+      <c r="G176">
+        <v>500</v>
+      </c>
+      <c r="H176">
+        <v>376</v>
+      </c>
+      <c r="I176">
+        <v>330</v>
+      </c>
+      <c r="J176">
+        <v>53</v>
+      </c>
+      <c r="K176">
+        <v>205.19</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>9532082</v>
+      </c>
+      <c r="B177" t="s">
+        <v>57</v>
+      </c>
+      <c r="C177">
+        <v>25</v>
+      </c>
+      <c r="D177">
+        <v>150</v>
+      </c>
+      <c r="E177">
+        <v>7.1</v>
+      </c>
+      <c r="F177">
+        <v>2.7E-2</v>
+      </c>
+      <c r="G177">
+        <v>365</v>
+      </c>
+      <c r="H177">
+        <v>276</v>
+      </c>
+      <c r="I177">
+        <v>315</v>
+      </c>
+      <c r="J177">
+        <v>25</v>
+      </c>
+      <c r="K177">
+        <v>257.23</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>9532082</v>
+      </c>
+      <c r="B178" t="s">
+        <v>57</v>
+      </c>
+      <c r="C178">
+        <v>50</v>
+      </c>
+      <c r="D178">
+        <v>300</v>
+      </c>
+      <c r="E178">
+        <v>10.3</v>
+      </c>
+      <c r="F178">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="G178">
+        <v>435</v>
+      </c>
+      <c r="H178">
+        <v>316</v>
+      </c>
+      <c r="I178">
+        <v>335</v>
+      </c>
+      <c r="J178">
+        <v>31</v>
+      </c>
+      <c r="K178">
+        <v>218.87</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>9532082</v>
+      </c>
+      <c r="B179" t="s">
+        <v>57</v>
+      </c>
+      <c r="C179">
+        <v>75</v>
+      </c>
+      <c r="D179">
+        <v>450</v>
+      </c>
+      <c r="E179">
+        <v>13.4</v>
+      </c>
+      <c r="F179">
+        <v>0.156</v>
+      </c>
+      <c r="G179">
+        <v>447.5</v>
+      </c>
+      <c r="H179">
+        <v>326</v>
+      </c>
+      <c r="I179">
+        <v>315</v>
+      </c>
+      <c r="J179">
+        <v>40</v>
+      </c>
+      <c r="K179">
+        <v>208.03</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>9532082</v>
+      </c>
+      <c r="B180" t="s">
+        <v>57</v>
+      </c>
+      <c r="C180">
+        <v>100</v>
+      </c>
+      <c r="D180">
+        <v>600</v>
+      </c>
+      <c r="E180">
+        <v>15.9</v>
+      </c>
+      <c r="F180">
+        <v>0.23</v>
+      </c>
+      <c r="G180">
+        <v>482.5</v>
+      </c>
+      <c r="H180">
+        <v>355</v>
+      </c>
+      <c r="I180">
+        <v>315</v>
+      </c>
+      <c r="J180">
+        <v>49</v>
+      </c>
+      <c r="K180">
+        <v>204.66</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>9532082</v>
+      </c>
+      <c r="B181" t="s">
+        <v>57</v>
+      </c>
+      <c r="C181">
+        <v>110</v>
+      </c>
+      <c r="D181">
+        <v>660</v>
+      </c>
+      <c r="E181">
+        <v>17.2</v>
+      </c>
+      <c r="F181">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="G181">
+        <v>502.5</v>
+      </c>
+      <c r="H181">
+        <v>368</v>
+      </c>
+      <c r="I181">
+        <v>320</v>
+      </c>
+      <c r="J181">
+        <v>52</v>
+      </c>
+      <c r="K181">
+        <v>205.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Aepms-backend/data/ae_shop_trial.xlsx
+++ b/Aepms-backend/data/ae_shop_trial.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/Aepms-backend/data/ae_shop_trial.xlsx
+++ b/Aepms-backend/data/ae_shop_trial.xlsx
@@ -8,20 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOKUL\Desktop\WORKPLACE\Workplace\Aepms-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A389AF-6726-4A53-A5E7-821C3412C7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63EC472-835E-44F8-8BC4-35973ECF1C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vessel_generators" sheetId="1" r:id="rId1"/>
     <sheet name="generator_baseline_data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="64">
   <si>
     <t>imo_number</t>
   </si>
@@ -195,6 +206,24 @@
   </si>
   <si>
     <t>1764FXJ</t>
+  </si>
+  <si>
+    <t>PAAE161795</t>
+  </si>
+  <si>
+    <t>PAAE161794</t>
+  </si>
+  <si>
+    <t>PAAE161793</t>
+  </si>
+  <si>
+    <t>WARTSILA</t>
+  </si>
+  <si>
+    <t>A4L20</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -660,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
@@ -1635,6 +1664,84 @@
         <v>900</v>
       </c>
     </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>9521813</v>
+      </c>
+      <c r="B38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" t="s">
+        <v>62</v>
+      </c>
+      <c r="F38">
+        <v>4</v>
+      </c>
+      <c r="G38">
+        <v>548</v>
+      </c>
+      <c r="H38">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>9521813</v>
+      </c>
+      <c r="B39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" t="s">
+        <v>62</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39">
+        <v>548</v>
+      </c>
+      <c r="H39">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>9521813</v>
+      </c>
+      <c r="B40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40" t="s">
+        <v>62</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40">
+        <v>680</v>
+      </c>
+      <c r="H40">
+        <v>900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1646,7 +1753,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K181"/>
+  <dimension ref="A1:K199"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13.33203125" customWidth="1"/>
@@ -7924,6 +8031,636 @@
         <v>205.19</v>
       </c>
     </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>9521813</v>
+      </c>
+      <c r="B182" t="s">
+        <v>58</v>
+      </c>
+      <c r="C182">
+        <v>25</v>
+      </c>
+      <c r="D182">
+        <v>139</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F182" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G182" t="s">
+        <v>53</v>
+      </c>
+      <c r="H182" s="3">
+        <v>321</v>
+      </c>
+      <c r="I182" s="3">
+        <v>319</v>
+      </c>
+      <c r="J182" s="3">
+        <v>12</v>
+      </c>
+      <c r="K182" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>9521813</v>
+      </c>
+      <c r="B183" t="s">
+        <v>58</v>
+      </c>
+      <c r="C183">
+        <v>50</v>
+      </c>
+      <c r="D183">
+        <v>273</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F183" s="3">
+        <v>1</v>
+      </c>
+      <c r="G183" t="s">
+        <v>53</v>
+      </c>
+      <c r="H183" s="3">
+        <v>342</v>
+      </c>
+      <c r="I183" s="3">
+        <v>344</v>
+      </c>
+      <c r="J183" s="3">
+        <v>16</v>
+      </c>
+      <c r="K183" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>9521813</v>
+      </c>
+      <c r="B184" t="s">
+        <v>58</v>
+      </c>
+      <c r="C184">
+        <v>75</v>
+      </c>
+      <c r="D184">
+        <v>408</v>
+      </c>
+      <c r="E184" s="3">
+        <v>12.8</v>
+      </c>
+      <c r="F184" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="G184" t="s">
+        <v>53</v>
+      </c>
+      <c r="H184" s="3">
+        <v>360</v>
+      </c>
+      <c r="I184" s="3">
+        <v>331</v>
+      </c>
+      <c r="J184" s="3">
+        <v>21</v>
+      </c>
+      <c r="K184" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>9521813</v>
+      </c>
+      <c r="B185" t="s">
+        <v>58</v>
+      </c>
+      <c r="C185">
+        <v>85</v>
+      </c>
+      <c r="D185">
+        <v>462</v>
+      </c>
+      <c r="E185" s="3">
+        <v>13.9</v>
+      </c>
+      <c r="F185" s="3">
+        <v>2</v>
+      </c>
+      <c r="G185" t="s">
+        <v>53</v>
+      </c>
+      <c r="H185" s="3">
+        <v>370</v>
+      </c>
+      <c r="I185" s="3">
+        <v>333</v>
+      </c>
+      <c r="J185" s="3">
+        <v>22</v>
+      </c>
+      <c r="K185" s="3">
+        <v>205.4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>9521813</v>
+      </c>
+      <c r="B186" t="s">
+        <v>58</v>
+      </c>
+      <c r="C186">
+        <v>100</v>
+      </c>
+      <c r="D186">
+        <v>545</v>
+      </c>
+      <c r="E186" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="F186" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="G186" t="s">
+        <v>53</v>
+      </c>
+      <c r="H186" s="3">
+        <v>385</v>
+      </c>
+      <c r="I186" s="3">
+        <v>330</v>
+      </c>
+      <c r="J186" s="3">
+        <v>24</v>
+      </c>
+      <c r="K186" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>9521813</v>
+      </c>
+      <c r="B187" t="s">
+        <v>58</v>
+      </c>
+      <c r="C187">
+        <v>110</v>
+      </c>
+      <c r="D187">
+        <v>599</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F187" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="G187" t="s">
+        <v>53</v>
+      </c>
+      <c r="H187" s="3">
+        <v>394</v>
+      </c>
+      <c r="I187" s="3">
+        <v>326</v>
+      </c>
+      <c r="J187" s="3">
+        <v>26</v>
+      </c>
+      <c r="K187" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>9521813</v>
+      </c>
+      <c r="B188" t="s">
+        <v>59</v>
+      </c>
+      <c r="C188">
+        <v>25</v>
+      </c>
+      <c r="D188">
+        <v>139</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F188" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="G188" t="s">
+        <v>53</v>
+      </c>
+      <c r="H188" s="3">
+        <v>316</v>
+      </c>
+      <c r="I188" s="3">
+        <v>332</v>
+      </c>
+      <c r="J188" s="3">
+        <v>12</v>
+      </c>
+      <c r="K188" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>9521813</v>
+      </c>
+      <c r="B189" t="s">
+        <v>59</v>
+      </c>
+      <c r="C189">
+        <v>50</v>
+      </c>
+      <c r="D189">
+        <v>273</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F189" s="3">
+        <v>1</v>
+      </c>
+      <c r="G189" t="s">
+        <v>53</v>
+      </c>
+      <c r="H189" s="3">
+        <v>339</v>
+      </c>
+      <c r="I189" s="3">
+        <v>350</v>
+      </c>
+      <c r="J189" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="K189" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>9521813</v>
+      </c>
+      <c r="B190" t="s">
+        <v>59</v>
+      </c>
+      <c r="C190">
+        <v>75</v>
+      </c>
+      <c r="D190">
+        <v>408</v>
+      </c>
+      <c r="E190" s="3">
+        <v>12.9</v>
+      </c>
+      <c r="F190" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="G190" t="s">
+        <v>53</v>
+      </c>
+      <c r="H190" s="3">
+        <v>360</v>
+      </c>
+      <c r="I190" s="3">
+        <v>340</v>
+      </c>
+      <c r="J190" s="3">
+        <v>21</v>
+      </c>
+      <c r="K190" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>9521813</v>
+      </c>
+      <c r="B191" t="s">
+        <v>59</v>
+      </c>
+      <c r="C191">
+        <v>85</v>
+      </c>
+      <c r="D191">
+        <v>462</v>
+      </c>
+      <c r="E191" s="3">
+        <v>14.2</v>
+      </c>
+      <c r="F191" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="G191" t="s">
+        <v>53</v>
+      </c>
+      <c r="H191" s="3">
+        <v>369</v>
+      </c>
+      <c r="I191" s="3">
+        <v>339</v>
+      </c>
+      <c r="J191" s="3">
+        <v>22</v>
+      </c>
+      <c r="K191" s="3">
+        <v>191.6</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>9521813</v>
+      </c>
+      <c r="B192" t="s">
+        <v>59</v>
+      </c>
+      <c r="C192">
+        <v>100</v>
+      </c>
+      <c r="D192">
+        <v>545</v>
+      </c>
+      <c r="E192" s="3">
+        <v>15.6</v>
+      </c>
+      <c r="F192" s="3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G192" t="s">
+        <v>53</v>
+      </c>
+      <c r="H192" s="3">
+        <v>381</v>
+      </c>
+      <c r="I192" s="3">
+        <v>335</v>
+      </c>
+      <c r="J192" s="3">
+        <v>24</v>
+      </c>
+      <c r="K192" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>9521813</v>
+      </c>
+      <c r="B193" t="s">
+        <v>59</v>
+      </c>
+      <c r="C193">
+        <v>110</v>
+      </c>
+      <c r="D193">
+        <v>599</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F193" s="3">
+        <v>2.6</v>
+      </c>
+      <c r="G193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H193" s="3">
+        <v>389</v>
+      </c>
+      <c r="I193" s="3">
+        <v>327</v>
+      </c>
+      <c r="J193" s="3">
+        <v>26</v>
+      </c>
+      <c r="K193" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>9521813</v>
+      </c>
+      <c r="B194" t="s">
+        <v>60</v>
+      </c>
+      <c r="C194">
+        <v>25</v>
+      </c>
+      <c r="D194">
+        <v>173</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F194" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="G194" t="s">
+        <v>53</v>
+      </c>
+      <c r="H194" s="3">
+        <v>317</v>
+      </c>
+      <c r="I194" s="3">
+        <v>327</v>
+      </c>
+      <c r="J194" s="3">
+        <v>13</v>
+      </c>
+      <c r="K194" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>9521813</v>
+      </c>
+      <c r="B195" t="s">
+        <v>60</v>
+      </c>
+      <c r="C195">
+        <v>50</v>
+      </c>
+      <c r="D195">
+        <v>337</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F195" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="G195" t="s">
+        <v>53</v>
+      </c>
+      <c r="H195" s="3">
+        <v>342</v>
+      </c>
+      <c r="I195" s="3">
+        <v>336</v>
+      </c>
+      <c r="J195" s="3">
+        <v>19</v>
+      </c>
+      <c r="K195" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>9521813</v>
+      </c>
+      <c r="B196" t="s">
+        <v>60</v>
+      </c>
+      <c r="C196">
+        <v>75</v>
+      </c>
+      <c r="D196">
+        <v>504</v>
+      </c>
+      <c r="E196" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="F196" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G196" t="s">
+        <v>53</v>
+      </c>
+      <c r="H196" s="3">
+        <v>360</v>
+      </c>
+      <c r="I196" s="3">
+        <v>316</v>
+      </c>
+      <c r="J196" s="3">
+        <v>24</v>
+      </c>
+      <c r="K196" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>9521813</v>
+      </c>
+      <c r="B197" t="s">
+        <v>60</v>
+      </c>
+      <c r="C197">
+        <v>85</v>
+      </c>
+      <c r="D197">
+        <v>570</v>
+      </c>
+      <c r="E197" s="3">
+        <v>15.9</v>
+      </c>
+      <c r="F197" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="G197" t="s">
+        <v>53</v>
+      </c>
+      <c r="H197" s="3">
+        <v>373</v>
+      </c>
+      <c r="I197" s="3">
+        <v>318</v>
+      </c>
+      <c r="J197" s="3">
+        <v>15</v>
+      </c>
+      <c r="K197" s="3">
+        <v>207.4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>9521813</v>
+      </c>
+      <c r="B198" t="s">
+        <v>60</v>
+      </c>
+      <c r="C198">
+        <v>100</v>
+      </c>
+      <c r="D198">
+        <v>671</v>
+      </c>
+      <c r="E198" s="3">
+        <v>17.3</v>
+      </c>
+      <c r="F198" s="3">
+        <v>3</v>
+      </c>
+      <c r="G198" t="s">
+        <v>53</v>
+      </c>
+      <c r="H198" s="3">
+        <v>394</v>
+      </c>
+      <c r="I198" s="3">
+        <v>319</v>
+      </c>
+      <c r="J198" s="3">
+        <v>28</v>
+      </c>
+      <c r="K198" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>9521813</v>
+      </c>
+      <c r="B199" t="s">
+        <v>60</v>
+      </c>
+      <c r="C199">
+        <v>110</v>
+      </c>
+      <c r="D199">
+        <v>743</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F199" s="3">
+        <v>3.4</v>
+      </c>
+      <c r="G199" t="s">
+        <v>53</v>
+      </c>
+      <c r="H199" s="3">
+        <v>409</v>
+      </c>
+      <c r="I199" s="3">
+        <v>321</v>
+      </c>
+      <c r="J199" s="3">
+        <v>31</v>
+      </c>
+      <c r="K199" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
